--- a/releases/evt-pre-20/2026-09-30-rev-d/Заказ_плат_и_монтаж/00_Условия_передачи/BOM_плат_для_монтажа.xlsx
+++ b/releases/evt-pre-20/2026-09-30-rev-d/Заказ_плат_и_монтаж/00_Условия_передачи/BOM_плат_для_монтажа.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR BOM" sheetId="1" r:id="R2787e33794f04fd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR DNP" sheetId="2" r:id="R50c9ac0e5fb14292"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MIC BOM" sheetId="3" r:id="R6d2fac5fc9cd4cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MAIN BOM" sheetId="4" r:id="Ra2c0e64162194372"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="5" r:id="Rbf47e3256d3748ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR BOM" sheetId="1" r:id="Rbf71a3b4f4b14778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR DNP" sheetId="2" r:id="R503dcbdc3f0144e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MIC BOM" sheetId="3" r:id="R6e1d367e3e2d4808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MAIN BOM" sheetId="4" r:id="R79aa01736290445c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="5" r:id="R4e421414b9864b80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1298,6 +1298,10 @@
     <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
@@ -1308,22 +1312,38 @@
       <x:c r="C1" s="2"/>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="7" t="str">
         <x:v>Ref</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
+        <x:v>Manufacturer</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>MPN</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="str">
+      <x:c r="E2" s="7" t="str">
         <x:v>Footprint</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
+      <x:c r="F2" s="7" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="str">
+      <x:c r="G2" s="7" t="str">
         <x:v>DNP</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Procurement_ID</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="str">
+        <x:v>Placement_MPN</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="31" customHeight="1">
@@ -1331,3293 +1351,6017 @@
         <x:v>C1</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="str">
+      <x:c r="E3" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D3" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="str"/>
+      <x:c r="F3" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="str"/>
+      <x:c r="H3" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I3" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="31" customHeight="1">
       <x:c r="A4" s="5" t="str">
         <x:v>C2</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="str">
+      <x:c r="E4" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="str"/>
+      <x:c r="F4" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" s="5" t="str"/>
+      <x:c r="H4" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="31" customHeight="1">
       <x:c r="A5" s="5" t="str">
         <x:v>C3</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str">
+      <x:c r="E5" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="str"/>
+      <x:c r="F5" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="str"/>
+      <x:c r="H5" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="31" customHeight="1">
       <x:c r="A6" s="5" t="str">
         <x:v>C4</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
+      <x:c r="E6" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="5" t="str"/>
+      <x:c r="F6" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="str"/>
+      <x:c r="H6" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="31" customHeight="1">
       <x:c r="A7" s="5" t="str">
         <x:v>C5</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str">
+      <x:c r="E7" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="str"/>
+      <x:c r="F7" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="str"/>
+      <x:c r="H7" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="31" customHeight="1">
       <x:c r="A8" s="5" t="str">
         <x:v>C6</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="str">
+      <x:c r="E8" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="5" t="str"/>
+      <x:c r="F8" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="str"/>
+      <x:c r="H8" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="31" customHeight="1">
       <x:c r="A9" s="5" t="str">
         <x:v>C7</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="str">
+      <x:c r="E9" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="str"/>
+      <x:c r="F9" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="str"/>
+      <x:c r="H9" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="31" customHeight="1">
       <x:c r="A10" s="5" t="str">
         <x:v>C8</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="str">
+      <x:c r="E10" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="str"/>
+      <x:c r="F10" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="str"/>
+      <x:c r="H10" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="31" customHeight="1">
       <x:c r="A11" s="5" t="str">
         <x:v>C9</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>GRM155R61C105KA12D</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
         <x:v>1 uF 16 V X5R</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="str">
+      <x:c r="E11" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="str"/>
+      <x:c r="F11" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="5" t="str"/>
+      <x:c r="H11" s="5" t="str">
+        <x:v>PR-072</x:v>
+      </x:c>
+      <x:c r="I11" s="5" t="str">
+        <x:v>GRM155R61C105KA12D</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="31" customHeight="1">
       <x:c r="A12" s="5" t="str">
         <x:v>C10</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D12" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C12" s="5" t="str">
+      <x:c r="E12" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D12" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="5" t="str"/>
+      <x:c r="F12" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="5" t="str"/>
+      <x:c r="H12" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I12" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="31" customHeight="1">
       <x:c r="A13" s="5" t="str">
         <x:v>C11</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="str">
+        <x:v>GRM155R61C105KA12D</x:v>
+      </x:c>
+      <x:c r="D13" s="5" t="str">
         <x:v>1 uF 16 V X5R</x:v>
       </x:c>
-      <x:c r="C13" s="5" t="str">
+      <x:c r="E13" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D13" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="5" t="str"/>
+      <x:c r="F13" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="5" t="str"/>
+      <x:c r="H13" s="5" t="str">
+        <x:v>PR-072</x:v>
+      </x:c>
+      <x:c r="I13" s="5" t="str">
+        <x:v>GRM155R61C105KA12D</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="31" customHeight="1">
       <x:c r="A14" s="5" t="str">
         <x:v>C12</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C14" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D14" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C14" s="5" t="str">
+      <x:c r="E14" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D14" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="5" t="str"/>
+      <x:c r="F14" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="5" t="str"/>
+      <x:c r="H14" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I14" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="31" customHeight="1">
       <x:c r="A15" s="5" t="str">
         <x:v>C13</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C15" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D15" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C15" s="5" t="str">
+      <x:c r="E15" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D15" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="5" t="str"/>
+      <x:c r="F15" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="5" t="str"/>
+      <x:c r="H15" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I15" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="31" customHeight="1">
       <x:c r="A16" s="5" t="str">
         <x:v>C14</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="str">
+        <x:v>GRM155R61A225KE15D</x:v>
+      </x:c>
+      <x:c r="D16" s="5" t="str">
         <x:v>2.2 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C16" s="5" t="str">
+      <x:c r="E16" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D16" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="5" t="str"/>
+      <x:c r="F16" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="str"/>
+      <x:c r="H16" s="5" t="str">
+        <x:v>PR-071</x:v>
+      </x:c>
+      <x:c r="I16" s="5" t="str">
+        <x:v>GRM155R61A225KE15D</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="31" customHeight="1">
       <x:c r="A17" s="5" t="str">
         <x:v>C15</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="str">
+        <x:v>GRM155R61A225KE15D</x:v>
+      </x:c>
+      <x:c r="D17" s="5" t="str">
         <x:v>2.2 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C17" s="5" t="str">
+      <x:c r="E17" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D17" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="5" t="str"/>
+      <x:c r="F17" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="5" t="str"/>
+      <x:c r="H17" s="5" t="str">
+        <x:v>PR-071</x:v>
+      </x:c>
+      <x:c r="I17" s="5" t="str">
+        <x:v>GRM155R61A225KE15D</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="31" customHeight="1">
       <x:c r="A18" s="5" t="str">
         <x:v>C18</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D18" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C18" s="5" t="str">
+      <x:c r="E18" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D18" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="5" t="str"/>
+      <x:c r="F18" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="5" t="str"/>
+      <x:c r="H18" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I18" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="31" customHeight="1">
       <x:c r="A19" s="5" t="str">
         <x:v>C19</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="str">
+        <x:v>GRM21BR61A226ME44L</x:v>
+      </x:c>
+      <x:c r="D19" s="5" t="str">
         <x:v>22 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C19" s="5" t="str">
+      <x:c r="E19" s="5" t="str">
         <x:v>Capacitor_SMD:C_0805_2012Metric</x:v>
       </x:c>
-      <x:c r="D19" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="5" t="str"/>
+      <x:c r="F19" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="5" t="str"/>
+      <x:c r="H19" s="5" t="str">
+        <x:v>PR-081</x:v>
+      </x:c>
+      <x:c r="I19" s="5" t="str">
+        <x:v>GRM21BR61A226ME44L</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="31" customHeight="1">
       <x:c r="A20" s="5" t="str">
         <x:v>C20</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D20" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C20" s="5" t="str">
+      <x:c r="E20" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D20" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" s="5" t="str"/>
+      <x:c r="F20" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="5" t="str"/>
+      <x:c r="H20" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I20" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="31" customHeight="1">
       <x:c r="A21" s="5" t="str">
         <x:v>C21</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C21" s="5" t="str">
+      <x:c r="E21" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D21" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="5" t="str"/>
+      <x:c r="F21" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="5" t="str"/>
+      <x:c r="H21" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I21" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="31" customHeight="1">
       <x:c r="A22" s="5" t="str">
         <x:v>C22</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="str">
+        <x:v>GRM155R61C105KA12D</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="str">
         <x:v>1 uF 16 V X5R</x:v>
       </x:c>
-      <x:c r="C22" s="5" t="str">
+      <x:c r="E22" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D22" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E22" s="5" t="str"/>
+      <x:c r="F22" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="5" t="str"/>
+      <x:c r="H22" s="5" t="str">
+        <x:v>PR-072</x:v>
+      </x:c>
+      <x:c r="I22" s="5" t="str">
+        <x:v>GRM155R61C105KA12D</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="31" customHeight="1">
       <x:c r="A23" s="5" t="str">
         <x:v>C23</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D23" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C23" s="5" t="str">
+      <x:c r="E23" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D23" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E23" s="5" t="str"/>
+      <x:c r="F23" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="5" t="str"/>
+      <x:c r="H23" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I23" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="31" customHeight="1">
       <x:c r="A24" s="5" t="str">
         <x:v>C24</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D24" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C24" s="5" t="str">
+      <x:c r="E24" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D24" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E24" s="5" t="str"/>
+      <x:c r="F24" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="5" t="str"/>
+      <x:c r="H24" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I24" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="31" customHeight="1">
       <x:c r="A25" s="5" t="str">
         <x:v>C25</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C25" s="5" t="str">
+      <x:c r="E25" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D25" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E25" s="5" t="str"/>
+      <x:c r="F25" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="5" t="str"/>
+      <x:c r="H25" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I25" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="31" customHeight="1">
       <x:c r="A26" s="5" t="str">
         <x:v>C26</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C26" s="5" t="str">
+      <x:c r="E26" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D26" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E26" s="5" t="str"/>
+      <x:c r="F26" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="5" t="str"/>
+      <x:c r="H26" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I26" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="31" customHeight="1">
       <x:c r="A27" s="5" t="str">
         <x:v>C27</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C27" s="5" t="str">
+      <x:c r="E27" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D27" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E27" s="5" t="str"/>
+      <x:c r="F27" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="5" t="str"/>
+      <x:c r="H27" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I27" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="31" customHeight="1">
       <x:c r="A28" s="5" t="str">
         <x:v>C28</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C28" s="5" t="str">
+      <x:c r="E28" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D28" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E28" s="5" t="str"/>
+      <x:c r="F28" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="5" t="str"/>
+      <x:c r="H28" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I28" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="31" customHeight="1">
       <x:c r="A29" s="5" t="str">
         <x:v>C29</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C29" s="5" t="str">
+      <x:c r="E29" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D29" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E29" s="5" t="str"/>
+      <x:c r="F29" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="5" t="str"/>
+      <x:c r="H29" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I29" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="31" customHeight="1">
       <x:c r="A30" s="5" t="str">
         <x:v>C30</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C30" s="5" t="str">
+      <x:c r="E30" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D30" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E30" s="5" t="str"/>
+      <x:c r="F30" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="5" t="str"/>
+      <x:c r="H30" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I30" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="31" customHeight="1">
       <x:c r="A31" s="5" t="str">
         <x:v>C31</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C31" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C31" s="5" t="str">
+      <x:c r="E31" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D31" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E31" s="5" t="str"/>
+      <x:c r="F31" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="5" t="str"/>
+      <x:c r="H31" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I31" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="31" customHeight="1">
       <x:c r="A32" s="5" t="str">
         <x:v>C32</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C32" s="5" t="str">
+      <x:c r="E32" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D32" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E32" s="5" t="str"/>
+      <x:c r="F32" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="5" t="str"/>
+      <x:c r="H32" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I32" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="31" customHeight="1">
       <x:c r="A33" s="5" t="str">
         <x:v>C33</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C33" s="5" t="str">
+      <x:c r="E33" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D33" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E33" s="5" t="str"/>
+      <x:c r="F33" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="5" t="str"/>
+      <x:c r="H33" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I33" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="31" customHeight="1">
       <x:c r="A34" s="5" t="str">
         <x:v>C34</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C34" s="5" t="str">
+      <x:c r="E34" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D34" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E34" s="5" t="str"/>
+      <x:c r="F34" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="5" t="str"/>
+      <x:c r="H34" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I34" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="31" customHeight="1">
       <x:c r="A35" s="5" t="str">
         <x:v>C35</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C35" s="5" t="str">
+      <x:c r="E35" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D35" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E35" s="5" t="str"/>
+      <x:c r="F35" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="5" t="str"/>
+      <x:c r="H35" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I35" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="31" customHeight="1">
       <x:c r="A36" s="5" t="str">
         <x:v>C36</x:v>
       </x:c>
       <x:c r="B36" s="5" t="str">
+        <x:v>KEMET</x:v>
+      </x:c>
+      <x:c r="C36" s="5" t="str">
+        <x:v>T520D107M006ATE015</x:v>
+      </x:c>
+      <x:c r="D36" s="5" t="str">
         <x:v>100 uF 6.3 V 15 mOhm polymer</x:v>
       </x:c>
-      <x:c r="C36" s="5" t="str"/>
-      <x:c r="D36" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E36" s="5" t="str"/>
+      <x:c r="F36" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="5" t="str"/>
+      <x:c r="H36" s="5" t="str">
+        <x:v>PR-111</x:v>
+      </x:c>
+      <x:c r="I36" s="5" t="str">
+        <x:v>T520D107M006ATE015</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="31" customHeight="1">
       <x:c r="A37" s="5" t="str">
         <x:v>C37</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="str">
+        <x:v>GRM155R71E224KE14D</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="str">
         <x:v>220 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C37" s="5" t="str">
+      <x:c r="E37" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D37" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E37" s="5" t="str"/>
+      <x:c r="F37" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="5" t="str"/>
+      <x:c r="H37" s="5" t="str">
+        <x:v>PR-077</x:v>
+      </x:c>
+      <x:c r="I37" s="5" t="str">
+        <x:v>GRM155R71E224KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="31" customHeight="1">
       <x:c r="A38" s="5" t="str">
         <x:v>C38</x:v>
       </x:c>
       <x:c r="B38" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C38" s="5" t="str">
+        <x:v>GRM155R71E473KA01D</x:v>
+      </x:c>
+      <x:c r="D38" s="5" t="str">
         <x:v>47 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C38" s="5" t="str">
+      <x:c r="E38" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D38" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E38" s="5" t="str"/>
+      <x:c r="F38" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" s="5" t="str"/>
+      <x:c r="H38" s="5" t="str">
+        <x:v>PR-078</x:v>
+      </x:c>
+      <x:c r="I38" s="5" t="str">
+        <x:v>GRM155R71E473KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="31" customHeight="1">
       <x:c r="A39" s="5" t="str">
         <x:v>C39</x:v>
       </x:c>
       <x:c r="B39" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="str">
+        <x:v>GRM1555C1H151JA01D</x:v>
+      </x:c>
+      <x:c r="D39" s="5" t="str">
         <x:v>150 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C39" s="5" t="str">
+      <x:c r="E39" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D39" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E39" s="5" t="str"/>
+      <x:c r="F39" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="5" t="str"/>
+      <x:c r="H39" s="5" t="str">
+        <x:v>PR-067</x:v>
+      </x:c>
+      <x:c r="I39" s="5" t="str">
+        <x:v>GRM1555C1H151JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="31" customHeight="1">
       <x:c r="A40" s="5" t="str">
         <x:v>C40</x:v>
       </x:c>
       <x:c r="B40" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C40" s="5" t="str">
+        <x:v>GRM1555C1H101JA01D</x:v>
+      </x:c>
+      <x:c r="D40" s="5" t="str">
         <x:v>100 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C40" s="5" t="str">
+      <x:c r="E40" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D40" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E40" s="5" t="str"/>
+      <x:c r="F40" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G40" s="5" t="str"/>
+      <x:c r="H40" s="5" t="str">
+        <x:v>PR-066</x:v>
+      </x:c>
+      <x:c r="I40" s="5" t="str">
+        <x:v>GRM1555C1H101JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="31" customHeight="1">
       <x:c r="A41" s="5" t="str">
         <x:v>C41</x:v>
       </x:c>
       <x:c r="B41" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C41" s="5" t="str">
+        <x:v>GRM1555C1H680JA01D</x:v>
+      </x:c>
+      <x:c r="D41" s="5" t="str">
         <x:v>68 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C41" s="5" t="str">
+      <x:c r="E41" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D41" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E41" s="5" t="str"/>
+      <x:c r="F41" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G41" s="5" t="str"/>
+      <x:c r="H41" s="5" t="str">
+        <x:v>PR-070</x:v>
+      </x:c>
+      <x:c r="I41" s="5" t="str">
+        <x:v>GRM1555C1H680JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="31" customHeight="1">
       <x:c r="A42" s="5" t="str">
         <x:v>C42</x:v>
       </x:c>
       <x:c r="B42" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C42" s="5" t="str">
+        <x:v>GRM1555C1H330JA01D</x:v>
+      </x:c>
+      <x:c r="D42" s="5" t="str">
         <x:v>33 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C42" s="5" t="str">
+      <x:c r="E42" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D42" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E42" s="5" t="str"/>
+      <x:c r="F42" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="5" t="str"/>
+      <x:c r="H42" s="5" t="str">
+        <x:v>PR-069</x:v>
+      </x:c>
+      <x:c r="I42" s="5" t="str">
+        <x:v>GRM1555C1H330JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="31" customHeight="1">
       <x:c r="A43" s="5" t="str">
         <x:v>C43</x:v>
       </x:c>
       <x:c r="B43" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C43" s="5" t="str">
+        <x:v>GRM1555C1H100JA01D</x:v>
+      </x:c>
+      <x:c r="D43" s="5" t="str">
         <x:v>10 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C43" s="5" t="str">
+      <x:c r="E43" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D43" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E43" s="5" t="str"/>
+      <x:c r="F43" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="5" t="str"/>
+      <x:c r="H43" s="5" t="str">
+        <x:v>PR-065</x:v>
+      </x:c>
+      <x:c r="I43" s="5" t="str">
+        <x:v>GRM1555C1H100JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="31" customHeight="1">
       <x:c r="A44" s="5" t="str">
         <x:v>C44</x:v>
       </x:c>
       <x:c r="B44" s="5" t="str">
+        <x:v>KEMET</x:v>
+      </x:c>
+      <x:c r="C44" s="5" t="str">
+        <x:v>T520D107M006ATE015</x:v>
+      </x:c>
+      <x:c r="D44" s="5" t="str">
         <x:v>100 uF 6.3 V 15 mOhm polymer</x:v>
       </x:c>
-      <x:c r="C44" s="5" t="str"/>
-      <x:c r="D44" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E44" s="5" t="str"/>
+      <x:c r="F44" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="5" t="str"/>
+      <x:c r="H44" s="5" t="str">
+        <x:v>PR-111</x:v>
+      </x:c>
+      <x:c r="I44" s="5" t="str">
+        <x:v>T520D107M006ATE015</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="31" customHeight="1">
       <x:c r="A45" s="5" t="str">
         <x:v>C45</x:v>
       </x:c>
       <x:c r="B45" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C45" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D45" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C45" s="5" t="str">
+      <x:c r="E45" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D45" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E45" s="5" t="str"/>
+      <x:c r="F45" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G45" s="5" t="str"/>
+      <x:c r="H45" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I45" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="31" customHeight="1">
       <x:c r="A46" s="5" t="str">
         <x:v>C46</x:v>
       </x:c>
       <x:c r="B46" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C46" s="5" t="str">
+        <x:v>GRM1555C1H330JA01D</x:v>
+      </x:c>
+      <x:c r="D46" s="5" t="str">
         <x:v>33 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C46" s="5" t="str">
+      <x:c r="E46" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D46" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E46" s="5" t="str"/>
+      <x:c r="F46" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G46" s="5" t="str"/>
+      <x:c r="H46" s="5" t="str">
+        <x:v>PR-069</x:v>
+      </x:c>
+      <x:c r="I46" s="5" t="str">
+        <x:v>GRM1555C1H330JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="31" customHeight="1">
       <x:c r="A47" s="5" t="str">
         <x:v>C47</x:v>
       </x:c>
       <x:c r="B47" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C47" s="5" t="str">
+        <x:v>GRM1555C1H100JA01D</x:v>
+      </x:c>
+      <x:c r="D47" s="5" t="str">
         <x:v>10 pF 50 V C0G</x:v>
       </x:c>
-      <x:c r="C47" s="5" t="str">
+      <x:c r="E47" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D47" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E47" s="5" t="str"/>
+      <x:c r="F47" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" s="5" t="str"/>
+      <x:c r="H47" s="5" t="str">
+        <x:v>PR-065</x:v>
+      </x:c>
+      <x:c r="I47" s="5" t="str">
+        <x:v>GRM1555C1H100JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="31" customHeight="1">
       <x:c r="A48" s="5" t="str">
         <x:v>C48</x:v>
       </x:c>
       <x:c r="B48" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C48" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
+      <x:c r="D48" s="5" t="str">
         <x:v>10 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C48" s="5" t="str">
+      <x:c r="E48" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D48" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E48" s="5" t="str"/>
+      <x:c r="F48" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" s="5" t="str"/>
+      <x:c r="H48" s="5" t="str">
+        <x:v>PR-074</x:v>
+      </x:c>
+      <x:c r="I48" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="31" customHeight="1">
       <x:c r="A49" s="5" t="str">
         <x:v>C49</x:v>
       </x:c>
       <x:c r="B49" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C49" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D49" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C49" s="5" t="str">
+      <x:c r="E49" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D49" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E49" s="5" t="str"/>
+      <x:c r="F49" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G49" s="5" t="str"/>
+      <x:c r="H49" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I49" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="31" customHeight="1">
       <x:c r="A50" s="5" t="str">
         <x:v>C50</x:v>
       </x:c>
       <x:c r="B50" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C50" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D50" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C50" s="5" t="str">
+      <x:c r="E50" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D50" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E50" s="5" t="str"/>
+      <x:c r="F50" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G50" s="5" t="str"/>
+      <x:c r="H50" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I50" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="31" customHeight="1">
       <x:c r="A51" s="5" t="str">
         <x:v>C51</x:v>
       </x:c>
       <x:c r="B51" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C51" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D51" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C51" s="5" t="str">
+      <x:c r="E51" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D51" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E51" s="5" t="str"/>
+      <x:c r="F51" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G51" s="5" t="str"/>
+      <x:c r="H51" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I51" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="31" customHeight="1">
       <x:c r="A52" s="5" t="str">
         <x:v>C52</x:v>
       </x:c>
       <x:c r="B52" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C52" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
+      <x:c r="D52" s="5" t="str">
         <x:v>10 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C52" s="5" t="str">
+      <x:c r="E52" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D52" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E52" s="5" t="str"/>
+      <x:c r="F52" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52" s="5" t="str"/>
+      <x:c r="H52" s="5" t="str">
+        <x:v>PR-074</x:v>
+      </x:c>
+      <x:c r="I52" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="31" customHeight="1">
       <x:c r="A53" s="5" t="str">
         <x:v>C53</x:v>
       </x:c>
       <x:c r="B53" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C53" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
+      <x:c r="D53" s="5" t="str">
         <x:v>10 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C53" s="5" t="str">
+      <x:c r="E53" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D53" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E53" s="5" t="str"/>
+      <x:c r="F53" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G53" s="5" t="str"/>
+      <x:c r="H53" s="5" t="str">
+        <x:v>PR-074</x:v>
+      </x:c>
+      <x:c r="I53" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="31" customHeight="1">
       <x:c r="A54" s="5" t="str">
         <x:v>C60</x:v>
       </x:c>
       <x:c r="B54" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C54" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D54" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C54" s="5" t="str">
+      <x:c r="E54" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D54" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E54" s="5" t="str"/>
+      <x:c r="F54" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54" s="5" t="str"/>
+      <x:c r="H54" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I54" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="31" customHeight="1">
       <x:c r="A55" s="5" t="str">
         <x:v>C61</x:v>
       </x:c>
       <x:c r="B55" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C55" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D55" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C55" s="5" t="str">
+      <x:c r="E55" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D55" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E55" s="5" t="str"/>
+      <x:c r="F55" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" s="5" t="str"/>
+      <x:c r="H55" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I55" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="31" customHeight="1">
       <x:c r="A56" s="5" t="str">
         <x:v>C62</x:v>
       </x:c>
       <x:c r="B56" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C56" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D56" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C56" s="5" t="str">
+      <x:c r="E56" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D56" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E56" s="5" t="str"/>
+      <x:c r="F56" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="5" t="str"/>
+      <x:c r="H56" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I56" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="31" customHeight="1">
       <x:c r="A57" s="5" t="str">
         <x:v>C63</x:v>
       </x:c>
       <x:c r="B57" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C57" s="5" t="str">
+        <x:v>GRM155R71C103KA01D</x:v>
+      </x:c>
+      <x:c r="D57" s="5" t="str">
         <x:v>10 nF 16 V X7R</x:v>
       </x:c>
-      <x:c r="C57" s="5" t="str">
+      <x:c r="E57" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D57" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E57" s="5" t="str"/>
+      <x:c r="F57" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57" s="5" t="str"/>
+      <x:c r="H57" s="5" t="str">
+        <x:v>PR-073</x:v>
+      </x:c>
+      <x:c r="I57" s="5" t="str">
+        <x:v>GRM155R71C103KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="31" customHeight="1">
       <x:c r="A58" s="5" t="str">
         <x:v>C64</x:v>
       </x:c>
       <x:c r="B58" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C58" s="5" t="str">
+        <x:v>GRM1555C1E470JA01D</x:v>
+      </x:c>
+      <x:c r="D58" s="5" t="str">
         <x:v>47 pF 25 V C0G</x:v>
       </x:c>
-      <x:c r="C58" s="5" t="str">
+      <x:c r="E58" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D58" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E58" s="5" t="str"/>
+      <x:c r="F58" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G58" s="5" t="str"/>
+      <x:c r="H58" s="5" t="str">
+        <x:v>PR-063</x:v>
+      </x:c>
+      <x:c r="I58" s="5" t="str">
+        <x:v>GRM1555C1E470JA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="31" customHeight="1">
       <x:c r="A59" s="5" t="str">
         <x:v>C65</x:v>
       </x:c>
       <x:c r="B59" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C59" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D59" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C59" s="5" t="str">
+      <x:c r="E59" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D59" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E59" s="5" t="str"/>
+      <x:c r="F59" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G59" s="5" t="str"/>
+      <x:c r="H59" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I59" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="31" customHeight="1">
       <x:c r="A60" s="5" t="str">
         <x:v>C66</x:v>
       </x:c>
       <x:c r="B60" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C60" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D60" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C60" s="5" t="str">
+      <x:c r="E60" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D60" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E60" s="5" t="str"/>
+      <x:c r="F60" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G60" s="5" t="str"/>
+      <x:c r="H60" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I60" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="31" customHeight="1">
       <x:c r="A61" s="5" t="str">
         <x:v>C67</x:v>
       </x:c>
       <x:c r="B61" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C61" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D61" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C61" s="5" t="str">
+      <x:c r="E61" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D61" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E61" s="5" t="str"/>
+      <x:c r="F61" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61" s="5" t="str"/>
+      <x:c r="H61" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I61" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="31" customHeight="1">
       <x:c r="A62" s="5" t="str">
         <x:v>C68</x:v>
       </x:c>
       <x:c r="B62" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C62" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D62" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C62" s="5" t="str">
+      <x:c r="E62" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D62" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E62" s="5" t="str"/>
+      <x:c r="F62" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G62" s="5" t="str"/>
+      <x:c r="H62" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I62" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="31" customHeight="1">
       <x:c r="A63" s="5" t="str">
         <x:v>C71</x:v>
       </x:c>
       <x:c r="B63" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C63" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D63" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C63" s="5" t="str">
+      <x:c r="E63" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D63" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E63" s="5" t="str"/>
+      <x:c r="F63" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63" s="5" t="str"/>
+      <x:c r="H63" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I63" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="31" customHeight="1">
       <x:c r="A64" s="5" t="str">
         <x:v>C72</x:v>
       </x:c>
       <x:c r="B64" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C64" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D64" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C64" s="5" t="str">
+      <x:c r="E64" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D64" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E64" s="5" t="str"/>
+      <x:c r="F64" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" s="5" t="str"/>
+      <x:c r="H64" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I64" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="31" customHeight="1">
       <x:c r="A65" s="5" t="str">
         <x:v>C73</x:v>
       </x:c>
       <x:c r="B65" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C65" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D65" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C65" s="5" t="str">
+      <x:c r="E65" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D65" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E65" s="5" t="str"/>
+      <x:c r="F65" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65" s="5" t="str"/>
+      <x:c r="H65" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I65" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="31" customHeight="1">
       <x:c r="A66" s="5" t="str">
         <x:v>C74</x:v>
       </x:c>
       <x:c r="B66" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C66" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
+      <x:c r="D66" s="5" t="str">
         <x:v>100 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C66" s="5" t="str">
+      <x:c r="E66" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D66" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E66" s="5" t="str"/>
+      <x:c r="F66" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66" s="5" t="str"/>
+      <x:c r="H66" s="5" t="str">
+        <x:v>PR-076</x:v>
+      </x:c>
+      <x:c r="I66" s="5" t="str">
+        <x:v>GRM155R71E104KE14D</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="31" customHeight="1">
       <x:c r="A67" s="5" t="str">
         <x:v>C75</x:v>
       </x:c>
       <x:c r="B67" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C67" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
+      <x:c r="D67" s="5" t="str">
         <x:v>10 uF 10 V X5R</x:v>
       </x:c>
-      <x:c r="C67" s="5" t="str">
+      <x:c r="E67" s="5" t="str">
         <x:v>Capacitor_SMD:C_0603_1608Metric</x:v>
       </x:c>
-      <x:c r="D67" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E67" s="5" t="str"/>
+      <x:c r="F67" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" s="5" t="str"/>
+      <x:c r="H67" s="5" t="str">
+        <x:v>PR-080</x:v>
+      </x:c>
+      <x:c r="I67" s="5" t="str">
+        <x:v>GRM188R61A106KE69D</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="31" customHeight="1">
       <x:c r="A68" s="5" t="str">
         <x:v>C76</x:v>
       </x:c>
       <x:c r="B68" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C68" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
+      <x:c r="D68" s="5" t="str">
         <x:v>10 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C68" s="5" t="str">
+      <x:c r="E68" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D68" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E68" s="5" t="str"/>
+      <x:c r="F68" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G68" s="5" t="str"/>
+      <x:c r="H68" s="5" t="str">
+        <x:v>PR-074</x:v>
+      </x:c>
+      <x:c r="I68" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="31" customHeight="1">
       <x:c r="A69" s="5" t="str">
         <x:v>C77</x:v>
       </x:c>
       <x:c r="B69" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C69" s="5" t="str">
+        <x:v>GRM155R72A472KA01D</x:v>
+      </x:c>
+      <x:c r="D69" s="5" t="str">
         <x:v>4.7 nF 100 V X7R</x:v>
       </x:c>
-      <x:c r="C69" s="5" t="str">
+      <x:c r="E69" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D69" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E69" s="5" t="str"/>
+      <x:c r="F69" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G69" s="5" t="str"/>
+      <x:c r="H69" s="5" t="str">
+        <x:v>PR-079</x:v>
+      </x:c>
+      <x:c r="I69" s="5" t="str">
+        <x:v>GRM155R72A472KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="31" customHeight="1">
       <x:c r="A70" s="5" t="str">
         <x:v>C78</x:v>
       </x:c>
       <x:c r="B70" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C70" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
+      <x:c r="D70" s="5" t="str">
         <x:v>10 nF 25 V X7R</x:v>
       </x:c>
-      <x:c r="C70" s="5" t="str">
+      <x:c r="E70" s="5" t="str">
         <x:v>Capacitor_SMD:C_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D70" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E70" s="5" t="str"/>
+      <x:c r="F70" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G70" s="5" t="str"/>
+      <x:c r="H70" s="5" t="str">
+        <x:v>PR-074</x:v>
+      </x:c>
+      <x:c r="I70" s="5" t="str">
+        <x:v>GRM155R71E103KA01D</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="31" customHeight="1">
       <x:c r="A71" s="5" t="str">
         <x:v>D1</x:v>
       </x:c>
       <x:c r="B71" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C71" s="5" t="str">
+        <x:v>PESD5V0S1UL</x:v>
+      </x:c>
+      <x:c r="D71" s="5" t="str">
         <x:v>5 V unidirectional 150 W TVS</x:v>
       </x:c>
-      <x:c r="C71" s="5" t="str"/>
-      <x:c r="D71" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E71" s="5" t="str"/>
+      <x:c r="F71" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G71" s="5" t="str"/>
+      <x:c r="H71" s="5" t="str">
+        <x:v>PR-096</x:v>
+      </x:c>
+      <x:c r="I71" s="5" t="str">
+        <x:v>PESD5V0S1UL</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="31" customHeight="1">
       <x:c r="A72" s="5" t="str">
         <x:v>D2</x:v>
       </x:c>
       <x:c r="B72" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C72" s="5" t="str">
+        <x:v>PESD5V0S1UL</x:v>
+      </x:c>
+      <x:c r="D72" s="5" t="str">
         <x:v>5 V unidirectional 150 W TVS</x:v>
       </x:c>
-      <x:c r="C72" s="5" t="str"/>
-      <x:c r="D72" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E72" s="5" t="str"/>
+      <x:c r="F72" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G72" s="5" t="str"/>
+      <x:c r="H72" s="5" t="str">
+        <x:v>PR-096</x:v>
+      </x:c>
+      <x:c r="I72" s="5" t="str">
+        <x:v>PESD5V0S1UL</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="31" customHeight="1">
       <x:c r="A73" s="5" t="str">
         <x:v>D3</x:v>
       </x:c>
       <x:c r="B73" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C73" s="5" t="str">
+        <x:v>PESD5V0C1BSF</x:v>
+      </x:c>
+      <x:c r="D73" s="5" t="str">
         <x:v>5 V bidirectional 0.2 pF RF ESD</x:v>
       </x:c>
-      <x:c r="C73" s="5" t="str"/>
-      <x:c r="D73" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E73" s="5" t="str"/>
+      <x:c r="F73" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G73" s="5" t="str"/>
+      <x:c r="H73" s="5" t="str">
+        <x:v>PR-095</x:v>
+      </x:c>
+      <x:c r="I73" s="5" t="str">
+        <x:v>PESD5V0C1BSF</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="31" customHeight="1">
       <x:c r="A74" s="5" t="str">
         <x:v>D4</x:v>
       </x:c>
       <x:c r="B74" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C74" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D74" s="5" t="str">
         <x:v>5.5 V unidirectional 0.5 pF RF ESD</x:v>
       </x:c>
-      <x:c r="C74" s="5" t="str"/>
-      <x:c r="D74" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E74" s="5" t="str"/>
+      <x:c r="F74" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G74" s="5" t="str"/>
+      <x:c r="H74" s="5" t="str">
+        <x:v>PR-114</x:v>
+      </x:c>
+      <x:c r="I74" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="31" customHeight="1">
       <x:c r="A75" s="5" t="str">
         <x:v>D5</x:v>
       </x:c>
       <x:c r="B75" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C75" s="5" t="str">
+        <x:v>PESD5V0C1BSF</x:v>
+      </x:c>
+      <x:c r="D75" s="5" t="str">
         <x:v>5 V bidirectional 0.2 pF RF ESD</x:v>
       </x:c>
-      <x:c r="C75" s="5" t="str"/>
-      <x:c r="D75" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E75" s="5" t="str"/>
+      <x:c r="F75" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G75" s="5" t="str"/>
+      <x:c r="H75" s="5" t="str">
+        <x:v>PR-095</x:v>
+      </x:c>
+      <x:c r="I75" s="5" t="str">
+        <x:v>PESD5V0C1BSF</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="31" customHeight="1">
       <x:c r="A76" s="5" t="str">
         <x:v>D6</x:v>
       </x:c>
       <x:c r="B76" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C76" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D76" s="5" t="str">
         <x:v>5.5 V 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C76" s="5" t="str"/>
-      <x:c r="D76" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E76" s="5" t="str"/>
+      <x:c r="F76" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76" s="5" t="str"/>
+      <x:c r="H76" s="5" t="str">
+        <x:v>PR-113</x:v>
+      </x:c>
+      <x:c r="I76" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="31" customHeight="1">
       <x:c r="A77" s="5" t="str">
         <x:v>D7</x:v>
       </x:c>
       <x:c r="B77" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C77" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D77" s="5" t="str">
         <x:v>5.5 V 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C77" s="5" t="str"/>
-      <x:c r="D77" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E77" s="5" t="str"/>
+      <x:c r="F77" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" s="5" t="str"/>
+      <x:c r="H77" s="5" t="str">
+        <x:v>PR-113</x:v>
+      </x:c>
+      <x:c r="I77" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="31" customHeight="1">
       <x:c r="A78" s="5" t="str">
         <x:v>D8</x:v>
       </x:c>
       <x:c r="B78" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C78" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D78" s="5" t="str">
         <x:v>5.5 V 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C78" s="5" t="str"/>
-      <x:c r="D78" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E78" s="5" t="str"/>
+      <x:c r="F78" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G78" s="5" t="str"/>
+      <x:c r="H78" s="5" t="str">
+        <x:v>PR-113</x:v>
+      </x:c>
+      <x:c r="I78" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="31" customHeight="1">
       <x:c r="A79" s="5" t="str">
         <x:v>D9</x:v>
       </x:c>
       <x:c r="B79" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C79" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D79" s="5" t="str">
         <x:v>5.5 V 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C79" s="5" t="str"/>
-      <x:c r="D79" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E79" s="5" t="str"/>
+      <x:c r="F79" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" s="5" t="str"/>
+      <x:c r="H79" s="5" t="str">
+        <x:v>PR-113</x:v>
+      </x:c>
+      <x:c r="I79" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="31" customHeight="1">
       <x:c r="A80" s="5" t="str">
         <x:v>D10</x:v>
       </x:c>
       <x:c r="B80" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C80" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D80" s="5" t="str">
         <x:v>5.5 V 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C80" s="5" t="str"/>
-      <x:c r="D80" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E80" s="5" t="str"/>
+      <x:c r="F80" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="5" t="str"/>
+      <x:c r="H80" s="5" t="str">
+        <x:v>PR-113</x:v>
+      </x:c>
+      <x:c r="I80" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="31" customHeight="1">
       <x:c r="A81" s="5" t="str">
         <x:v>D11</x:v>
       </x:c>
       <x:c r="B81" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C81" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
+      <x:c r="D81" s="5" t="str">
         <x:v>5.5 V 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C81" s="5" t="str"/>
-      <x:c r="D81" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E81" s="5" t="str"/>
+      <x:c r="F81" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="5" t="str"/>
+      <x:c r="H81" s="5" t="str">
+        <x:v>PR-113</x:v>
+      </x:c>
+      <x:c r="I81" s="5" t="str">
+        <x:v>TPD1E05U06DYAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="31" customHeight="1">
       <x:c r="A82" s="5" t="str">
         <x:v>FB1</x:v>
       </x:c>
       <x:c r="B82" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C82" s="5" t="str">
+        <x:v>BLM31KN601SN1L</x:v>
+      </x:c>
+      <x:c r="D82" s="5" t="str">
         <x:v>600 Ohm at 100 MHz</x:v>
       </x:c>
-      <x:c r="C82" s="5" t="str">
+      <x:c r="E82" s="5" t="str">
         <x:v>Inductor_SMD:L_1206_3216Metric</x:v>
       </x:c>
-      <x:c r="D82" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E82" s="5" t="str"/>
+      <x:c r="F82" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82" s="5" t="str"/>
+      <x:c r="H82" s="5" t="str">
+        <x:v>PR-025</x:v>
+      </x:c>
+      <x:c r="I82" s="5" t="str">
+        <x:v>BLM31KN601SN1L</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="31" customHeight="1">
       <x:c r="A83" s="5" t="str">
         <x:v>FL1</x:v>
       </x:c>
       <x:c r="B83" s="5" t="str">
+        <x:v>Abracon</x:v>
+      </x:c>
+      <x:c r="C83" s="5" t="str">
+        <x:v>ABSES5AF-L100KM</x:v>
+      </x:c>
+      <x:c r="D83" s="5" t="str">
         <x:v>1582.4 MHz wideband GNSS SAW</x:v>
       </x:c>
-      <x:c r="C83" s="5" t="str"/>
-      <x:c r="D83" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E83" s="5" t="str"/>
+      <x:c r="F83" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="5" t="str"/>
+      <x:c r="H83" s="5" t="str">
+        <x:v>PR-023</x:v>
+      </x:c>
+      <x:c r="I83" s="5" t="str">
+        <x:v>ABSES5AF-L100KM</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="31" customHeight="1">
       <x:c r="A84" s="5" t="str">
         <x:v>J6</x:v>
       </x:c>
       <x:c r="B84" s="5" t="str">
+        <x:v>TE Connectivity</x:v>
+      </x:c>
+      <x:c r="C84" s="5" t="str">
         <x:v>2336582-1</x:v>
       </x:c>
-      <x:c r="C84" s="5" t="str"/>
       <x:c r="D84" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>2336582-1</x:v>
       </x:c>
       <x:c r="E84" s="5" t="str"/>
+      <x:c r="F84" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="5" t="str"/>
+      <x:c r="H84" s="5" t="str">
+        <x:v>PR-012</x:v>
+      </x:c>
+      <x:c r="I84" s="5" t="str">
+        <x:v>2336582-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="31" customHeight="1">
       <x:c r="A85" s="5" t="str">
         <x:v>J7</x:v>
       </x:c>
       <x:c r="B85" s="5" t="str">
+        <x:v>TE Connectivity</x:v>
+      </x:c>
+      <x:c r="C85" s="5" t="str">
         <x:v>2336582-1</x:v>
       </x:c>
-      <x:c r="C85" s="5" t="str"/>
       <x:c r="D85" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>2336582-1</x:v>
       </x:c>
       <x:c r="E85" s="5" t="str"/>
+      <x:c r="F85" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" s="5" t="str"/>
+      <x:c r="H85" s="5" t="str">
+        <x:v>PR-012</x:v>
+      </x:c>
+      <x:c r="I85" s="5" t="str">
+        <x:v>2336582-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="31" customHeight="1">
       <x:c r="A86" s="5" t="str">
         <x:v>J8</x:v>
       </x:c>
       <x:c r="B86" s="5" t="str">
+        <x:v>Hirose</x:v>
+      </x:c>
+      <x:c r="C86" s="5" t="str">
         <x:v>U.FL-R-SMT-1(60)</x:v>
       </x:c>
-      <x:c r="C86" s="5" t="str"/>
       <x:c r="D86" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>U.FL-R-SMT-1(60)</x:v>
       </x:c>
       <x:c r="E86" s="5" t="str"/>
+      <x:c r="F86" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" s="5" t="str"/>
+      <x:c r="H86" s="5" t="str">
+        <x:v>PR-119</x:v>
+      </x:c>
+      <x:c r="I86" s="5" t="str">
+        <x:v>U.FL-R-SMT-1(60)</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="31" customHeight="1">
       <x:c r="A87" s="5" t="str">
         <x:v>J9</x:v>
       </x:c>
       <x:c r="B87" s="5" t="str">
+        <x:v>Hirose</x:v>
+      </x:c>
+      <x:c r="C87" s="5" t="str">
         <x:v>U.FL-R-SMT-1(60)</x:v>
       </x:c>
-      <x:c r="C87" s="5" t="str"/>
       <x:c r="D87" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>U.FL-R-SMT-1(60)</x:v>
       </x:c>
       <x:c r="E87" s="5" t="str"/>
+      <x:c r="F87" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="5" t="str"/>
+      <x:c r="H87" s="5" t="str">
+        <x:v>PR-119</x:v>
+      </x:c>
+      <x:c r="I87" s="5" t="str">
+        <x:v>U.FL-R-SMT-1(60)</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="31" customHeight="1">
       <x:c r="A88" s="5" t="str">
         <x:v>J10</x:v>
       </x:c>
       <x:c r="B88" s="5" t="str">
+        <x:v>Hirose</x:v>
+      </x:c>
+      <x:c r="C88" s="5" t="str">
         <x:v>U.FL-R-SMT-1(60)</x:v>
       </x:c>
-      <x:c r="C88" s="5" t="str"/>
       <x:c r="D88" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>U.FL-R-SMT-1(60)</x:v>
       </x:c>
       <x:c r="E88" s="5" t="str"/>
+      <x:c r="F88" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" s="5" t="str"/>
+      <x:c r="H88" s="5" t="str">
+        <x:v>PR-120</x:v>
+      </x:c>
+      <x:c r="I88" s="5" t="str">
+        <x:v>U.FL-R-SMT-1(60)</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="31" customHeight="1">
       <x:c r="A89" s="5" t="str">
         <x:v>J11</x:v>
       </x:c>
       <x:c r="B89" s="5" t="str">
+        <x:v>GCT</x:v>
+      </x:c>
+      <x:c r="C89" s="5" t="str">
         <x:v>USB4105-GF-A-120</x:v>
       </x:c>
-      <x:c r="C89" s="5" t="str"/>
       <x:c r="D89" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>USB4105-GF-A-120</x:v>
       </x:c>
       <x:c r="E89" s="5" t="str"/>
+      <x:c r="F89" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="5" t="str"/>
+      <x:c r="H89" s="5" t="str">
+        <x:v>PR-121</x:v>
+      </x:c>
+      <x:c r="I89" s="5" t="str">
+        <x:v>USB4105-GF-A-120</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="31" customHeight="1">
       <x:c r="A90" s="5" t="str">
         <x:v>J12</x:v>
       </x:c>
       <x:c r="B90" s="5" t="str">
+        <x:v>GCT</x:v>
+      </x:c>
+      <x:c r="C90" s="5" t="str">
         <x:v>MEM2052-00-195-00-A</x:v>
       </x:c>
-      <x:c r="C90" s="5" t="str"/>
       <x:c r="D90" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>MEM2052-00-195-00-A</x:v>
       </x:c>
       <x:c r="E90" s="5" t="str"/>
+      <x:c r="F90" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="5" t="str"/>
+      <x:c r="H90" s="5" t="str">
+        <x:v>PR-091</x:v>
+      </x:c>
+      <x:c r="I90" s="5" t="str">
+        <x:v>MEM2052-00-195-00-A</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" ht="31" customHeight="1">
       <x:c r="A91" s="5" t="str">
         <x:v>J13</x:v>
       </x:c>
       <x:c r="B91" s="5" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="C91" s="5" t="str">
+        <x:v>5040500291</x:v>
+      </x:c>
+      <x:c r="D91" s="5" t="str">
         <x:v>504050-0291</x:v>
       </x:c>
-      <x:c r="C91" s="5" t="str"/>
-      <x:c r="D91" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E91" s="5" t="str"/>
+      <x:c r="F91" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="5" t="str"/>
+      <x:c r="H91" s="5" t="str">
+        <x:v>PR-018</x:v>
+      </x:c>
+      <x:c r="I91" s="5" t="str">
+        <x:v>504050-0291</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="31" customHeight="1">
       <x:c r="A92" s="5" t="str">
         <x:v>J_MIC1</x:v>
       </x:c>
       <x:c r="B92" s="5" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="C92" s="5" t="str">
+        <x:v>5040500691</x:v>
+      </x:c>
+      <x:c r="D92" s="5" t="str">
         <x:v>504050-0691</x:v>
       </x:c>
-      <x:c r="C92" s="5" t="str"/>
-      <x:c r="D92" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E92" s="5" t="str"/>
+      <x:c r="F92" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="5" t="str"/>
+      <x:c r="H92" s="5" t="str">
+        <x:v>PR-019</x:v>
+      </x:c>
+      <x:c r="I92" s="5" t="str">
+        <x:v>504050-0691</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="31" customHeight="1">
       <x:c r="A93" s="5" t="str">
         <x:v>J_MIC2</x:v>
       </x:c>
       <x:c r="B93" s="5" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="C93" s="5" t="str">
+        <x:v>5040500691</x:v>
+      </x:c>
+      <x:c r="D93" s="5" t="str">
         <x:v>504050-0691</x:v>
       </x:c>
-      <x:c r="C93" s="5" t="str"/>
-      <x:c r="D93" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E93" s="5" t="str"/>
+      <x:c r="F93" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G93" s="5" t="str"/>
+      <x:c r="H93" s="5" t="str">
+        <x:v>PR-019</x:v>
+      </x:c>
+      <x:c r="I93" s="5" t="str">
+        <x:v>504050-0691</x:v>
+      </x:c>
     </x:row>
     <x:row r="94" ht="31" customHeight="1">
       <x:c r="A94" s="5" t="str">
         <x:v>J_MIC3</x:v>
       </x:c>
       <x:c r="B94" s="5" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="C94" s="5" t="str">
+        <x:v>5040500691</x:v>
+      </x:c>
+      <x:c r="D94" s="5" t="str">
         <x:v>504050-0691</x:v>
       </x:c>
-      <x:c r="C94" s="5" t="str"/>
-      <x:c r="D94" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E94" s="5" t="str"/>
+      <x:c r="F94" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="5" t="str"/>
+      <x:c r="H94" s="5" t="str">
+        <x:v>PR-019</x:v>
+      </x:c>
+      <x:c r="I94" s="5" t="str">
+        <x:v>504050-0691</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" ht="31" customHeight="1">
       <x:c r="A95" s="5" t="str">
         <x:v>J_MIC4</x:v>
       </x:c>
       <x:c r="B95" s="5" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="C95" s="5" t="str">
+        <x:v>5040500691</x:v>
+      </x:c>
+      <x:c r="D95" s="5" t="str">
         <x:v>504050-0691</x:v>
       </x:c>
-      <x:c r="C95" s="5" t="str"/>
-      <x:c r="D95" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E95" s="5" t="str"/>
+      <x:c r="F95" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95" s="5" t="str"/>
+      <x:c r="H95" s="5" t="str">
+        <x:v>PR-019</x:v>
+      </x:c>
+      <x:c r="I95" s="5" t="str">
+        <x:v>504050-0691</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="31" customHeight="1">
       <x:c r="A96" s="5" t="str">
         <x:v>J_PWR1</x:v>
       </x:c>
       <x:c r="B96" s="5" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="C96" s="5" t="str">
+        <x:v>430451202</x:v>
+      </x:c>
+      <x:c r="D96" s="5" t="str">
         <x:v>43045-1202</x:v>
       </x:c>
-      <x:c r="C96" s="5" t="str"/>
-      <x:c r="D96" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E96" s="5" t="str"/>
+      <x:c r="F96" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G96" s="5" t="str"/>
+      <x:c r="H96" s="5" t="str">
+        <x:v>PR-017</x:v>
+      </x:c>
+      <x:c r="I96" s="5" t="str">
+        <x:v>43045-1202</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" ht="31" customHeight="1">
       <x:c r="A97" s="5" t="str">
         <x:v>L1</x:v>
       </x:c>
       <x:c r="B97" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C97" s="5" t="str">
+        <x:v>LQH32PN2R2NN0L</x:v>
+      </x:c>
+      <x:c r="D97" s="5" t="str">
         <x:v>2.2 uH 20%</x:v>
       </x:c>
-      <x:c r="C97" s="5" t="str">
+      <x:c r="E97" s="5" t="str">
         <x:v>Inductor_SMD:L_1210_3225Metric</x:v>
       </x:c>
-      <x:c r="D97" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E97" s="5" t="str"/>
+      <x:c r="F97" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G97" s="5" t="str"/>
+      <x:c r="H97" s="5" t="str">
+        <x:v>PR-086</x:v>
+      </x:c>
+      <x:c r="I97" s="5" t="str">
+        <x:v>LQH32PN2R2NN0L</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" ht="31" customHeight="1">
       <x:c r="A98" s="5" t="str">
         <x:v>L2</x:v>
       </x:c>
       <x:c r="B98" s="5" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="C98" s="5" t="str">
+        <x:v>LQW15AN27NJ00D</x:v>
+      </x:c>
+      <x:c r="D98" s="5" t="str">
         <x:v>27 nH 5%</x:v>
       </x:c>
-      <x:c r="C98" s="5" t="str">
+      <x:c r="E98" s="5" t="str">
         <x:v>Inductor_SMD:L_0402_1005Metric</x:v>
       </x:c>
-      <x:c r="D98" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E98" s="5" t="str"/>
+      <x:c r="F98" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" s="5" t="str"/>
+      <x:c r="H98" s="5" t="str">
+        <x:v>PR-087</x:v>
+      </x:c>
+      <x:c r="I98" s="5" t="str">
+        <x:v>LQW15AN27NJ00D</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" ht="31" customHeight="1">
       <x:c r="A99" s="5" t="str">
         <x:v>Q1</x:v>
       </x:c>
       <x:c r="B99" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C99" s="5" t="str">
         <x:v>MMBT3904,215</x:v>
       </x:c>
-      <x:c r="C99" s="5" t="str"/>
       <x:c r="D99" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>MMBT3904,215</x:v>
       </x:c>
       <x:c r="E99" s="5" t="str"/>
+      <x:c r="F99" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" s="5" t="str"/>
+      <x:c r="H99" s="5" t="str">
+        <x:v>PR-092</x:v>
+      </x:c>
+      <x:c r="I99" s="5" t="str">
+        <x:v>MMBT3904,215</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="31" customHeight="1">
       <x:c r="A100" s="5" t="str">
         <x:v>Q2</x:v>
       </x:c>
       <x:c r="B100" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C100" s="5" t="str">
         <x:v>MMBT3904,215</x:v>
       </x:c>
-      <x:c r="C100" s="5" t="str"/>
       <x:c r="D100" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>MMBT3904,215</x:v>
       </x:c>
       <x:c r="E100" s="5" t="str"/>
+      <x:c r="F100" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" s="5" t="str"/>
+      <x:c r="H100" s="5" t="str">
+        <x:v>PR-092</x:v>
+      </x:c>
+      <x:c r="I100" s="5" t="str">
+        <x:v>MMBT3904,215</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="31" customHeight="1">
       <x:c r="A101" s="5" t="str">
         <x:v>Q3</x:v>
       </x:c>
       <x:c r="B101" s="5" t="str">
+        <x:v>Nexperia</x:v>
+      </x:c>
+      <x:c r="C101" s="5" t="str">
         <x:v>MMBT3904,215</x:v>
       </x:c>
-      <x:c r="C101" s="5" t="str"/>
       <x:c r="D101" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>MMBT3904,215</x:v>
       </x:c>
       <x:c r="E101" s="5" t="str"/>
+      <x:c r="F101" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" s="5" t="str"/>
+      <x:c r="H101" s="5" t="str">
+        <x:v>PR-092</x:v>
+      </x:c>
+      <x:c r="I101" s="5" t="str">
+        <x:v>MMBT3904,215</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="31" customHeight="1">
       <x:c r="A102" s="5" t="str">
         <x:v>Q4</x:v>
       </x:c>
       <x:c r="B102" s="5" t="str">
+        <x:v>Vishay</x:v>
+      </x:c>
+      <x:c r="C102" s="5" t="str">
+        <x:v>Si1016X-T1-GE3</x:v>
+      </x:c>
+      <x:c r="D102" s="5" t="str">
         <x:v>Complementary N and P channel 20 V</x:v>
       </x:c>
-      <x:c r="C102" s="5" t="str"/>
-      <x:c r="D102" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E102" s="5" t="str"/>
+      <x:c r="F102" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G102" s="5" t="str"/>
+      <x:c r="H102" s="5" t="str">
+        <x:v>PR-109</x:v>
+      </x:c>
+      <x:c r="I102" s="5" t="str">
+        <x:v>Si1016X-T1-GE3</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="31" customHeight="1">
       <x:c r="A103" s="5" t="str">
         <x:v>R1</x:v>
       </x:c>
       <x:c r="B103" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C103" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D103" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C103" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D103" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E103" s="5" t="str"/>
+      <x:c r="E103" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F103" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G103" s="5" t="str"/>
+      <x:c r="H103" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I103" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="31" customHeight="1">
       <x:c r="A104" s="5" t="str">
         <x:v>R2</x:v>
       </x:c>
       <x:c r="B104" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C104" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D104" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C104" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D104" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E104" s="5" t="str"/>
+      <x:c r="E104" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F104" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" s="5" t="str"/>
+      <x:c r="H104" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I104" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="31" customHeight="1">
       <x:c r="A105" s="5" t="str">
         <x:v>R3</x:v>
       </x:c>
       <x:c r="B105" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C105" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D105" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C105" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D105" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E105" s="5" t="str"/>
+      <x:c r="E105" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F105" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" s="5" t="str"/>
+      <x:c r="H105" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I105" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="31" customHeight="1">
       <x:c r="A106" s="5" t="str">
         <x:v>R5</x:v>
       </x:c>
       <x:c r="B106" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C106" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D106" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C106" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D106" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E106" s="5" t="str"/>
+      <x:c r="E106" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F106" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" s="5" t="str"/>
+      <x:c r="H106" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I106" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="31" customHeight="1">
       <x:c r="A107" s="5" t="str">
         <x:v>R7</x:v>
       </x:c>
       <x:c r="B107" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C107" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D107" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C107" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D107" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E107" s="5" t="str"/>
+      <x:c r="E107" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F107" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="5" t="str"/>
+      <x:c r="H107" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I107" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" ht="31" customHeight="1">
       <x:c r="A108" s="5" t="str">
         <x:v>R8</x:v>
       </x:c>
       <x:c r="B108" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C108" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D108" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C108" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D108" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E108" s="5" t="str"/>
+      <x:c r="E108" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F108" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="5" t="str"/>
+      <x:c r="H108" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I108" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="31" customHeight="1">
       <x:c r="A109" s="5" t="str">
         <x:v>R9</x:v>
       </x:c>
       <x:c r="B109" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C109" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D109" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C109" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D109" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E109" s="5" t="str"/>
+      <x:c r="E109" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F109" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="5" t="str"/>
+      <x:c r="H109" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I109" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="31" customHeight="1">
       <x:c r="A110" s="5" t="str">
         <x:v>R10</x:v>
       </x:c>
       <x:c r="B110" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C110" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D110" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C110" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D110" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E110" s="5" t="str"/>
+      <x:c r="E110" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F110" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" s="5" t="str"/>
+      <x:c r="H110" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I110" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="31" customHeight="1">
       <x:c r="A111" s="5" t="str">
         <x:v>R11</x:v>
       </x:c>
       <x:c r="B111" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C111" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D111" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C111" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D111" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E111" s="5" t="str"/>
+      <x:c r="E111" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F111" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111" s="5" t="str"/>
+      <x:c r="H111" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I111" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" ht="31" customHeight="1">
       <x:c r="A112" s="5" t="str">
         <x:v>R12</x:v>
       </x:c>
       <x:c r="B112" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C112" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D112" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C112" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D112" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E112" s="5" t="str"/>
+      <x:c r="E112" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F112" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" s="5" t="str"/>
+      <x:c r="H112" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I112" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" ht="31" customHeight="1">
       <x:c r="A113" s="5" t="str">
         <x:v>R13</x:v>
       </x:c>
       <x:c r="B113" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C113" s="5" t="str">
+        <x:v>ERJ-2RKF2201X</x:v>
+      </x:c>
+      <x:c r="D113" s="5" t="str">
         <x:v>2.2 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C113" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D113" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E113" s="5" t="str"/>
+      <x:c r="E113" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F113" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" s="5" t="str"/>
+      <x:c r="H113" s="5" t="str">
+        <x:v>PR-054</x:v>
+      </x:c>
+      <x:c r="I113" s="5" t="str">
+        <x:v>ERJ-2RKF2201X</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" ht="31" customHeight="1">
       <x:c r="A114" s="5" t="str">
         <x:v>R14</x:v>
       </x:c>
       <x:c r="B114" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C114" s="5" t="str">
+        <x:v>ERJ-2RKF2201X</x:v>
+      </x:c>
+      <x:c r="D114" s="5" t="str">
         <x:v>2.2 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C114" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D114" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E114" s="5" t="str"/>
+      <x:c r="E114" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F114" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="5" t="str"/>
+      <x:c r="H114" s="5" t="str">
+        <x:v>PR-054</x:v>
+      </x:c>
+      <x:c r="I114" s="5" t="str">
+        <x:v>ERJ-2RKF2201X</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="31" customHeight="1">
       <x:c r="A115" s="5" t="str">
         <x:v>R15</x:v>
       </x:c>
       <x:c r="B115" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C115" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D115" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C115" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D115" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E115" s="5" t="str"/>
+      <x:c r="E115" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F115" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" s="5" t="str"/>
+      <x:c r="H115" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I115" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="31" customHeight="1">
       <x:c r="A116" s="5" t="str">
         <x:v>R16</x:v>
       </x:c>
       <x:c r="B116" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C116" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D116" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C116" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D116" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E116" s="5" t="str"/>
+      <x:c r="E116" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F116" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G116" s="5" t="str"/>
+      <x:c r="H116" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I116" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="31" customHeight="1">
       <x:c r="A117" s="5" t="str">
         <x:v>R17</x:v>
       </x:c>
       <x:c r="B117" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C117" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D117" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C117" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D117" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E117" s="5" t="str"/>
+      <x:c r="E117" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F117" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G117" s="5" t="str"/>
+      <x:c r="H117" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I117" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="31" customHeight="1">
       <x:c r="A118" s="5" t="str">
         <x:v>R18</x:v>
       </x:c>
       <x:c r="B118" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C118" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D118" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C118" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D118" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E118" s="5" t="str"/>
+      <x:c r="E118" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F118" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G118" s="5" t="str"/>
+      <x:c r="H118" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I118" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" ht="31" customHeight="1">
       <x:c r="A119" s="5" t="str">
         <x:v>R19</x:v>
       </x:c>
       <x:c r="B119" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C119" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D119" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C119" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D119" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E119" s="5" t="str"/>
+      <x:c r="E119" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F119" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G119" s="5" t="str"/>
+      <x:c r="H119" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I119" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="31" customHeight="1">
       <x:c r="A120" s="5" t="str">
         <x:v>R20</x:v>
       </x:c>
       <x:c r="B120" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C120" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D120" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C120" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D120" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E120" s="5" t="str"/>
+      <x:c r="E120" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F120" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G120" s="5" t="str"/>
+      <x:c r="H120" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I120" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" ht="31" customHeight="1">
       <x:c r="A121" s="5" t="str">
         <x:v>R21</x:v>
       </x:c>
       <x:c r="B121" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C121" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D121" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C121" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D121" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E121" s="5" t="str"/>
+      <x:c r="E121" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F121" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G121" s="5" t="str"/>
+      <x:c r="H121" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I121" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" ht="31" customHeight="1">
       <x:c r="A122" s="5" t="str">
         <x:v>R22</x:v>
       </x:c>
       <x:c r="B122" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C122" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D122" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C122" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D122" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E122" s="5" t="str"/>
+      <x:c r="E122" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F122" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G122" s="5" t="str"/>
+      <x:c r="H122" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I122" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" ht="31" customHeight="1">
       <x:c r="A123" s="5" t="str">
         <x:v>R23</x:v>
       </x:c>
       <x:c r="B123" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C123" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D123" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C123" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D123" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E123" s="5" t="str"/>
+      <x:c r="E123" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F123" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G123" s="5" t="str"/>
+      <x:c r="H123" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I123" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" ht="31" customHeight="1">
       <x:c r="A124" s="5" t="str">
         <x:v>R24</x:v>
       </x:c>
       <x:c r="B124" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C124" s="5" t="str">
+        <x:v>ERJ-2RKF4701X</x:v>
+      </x:c>
+      <x:c r="D124" s="5" t="str">
         <x:v>4.7 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C124" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D124" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E124" s="5" t="str"/>
+      <x:c r="E124" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F124" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G124" s="5" t="str"/>
+      <x:c r="H124" s="5" t="str">
+        <x:v>PR-056</x:v>
+      </x:c>
+      <x:c r="I124" s="5" t="str">
+        <x:v>ERJ-2RKF4701X</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" ht="31" customHeight="1">
       <x:c r="A125" s="5" t="str">
         <x:v>R25</x:v>
       </x:c>
       <x:c r="B125" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C125" s="5" t="str">
+        <x:v>ERJ-2RKF4702X</x:v>
+      </x:c>
+      <x:c r="D125" s="5" t="str">
         <x:v>47 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C125" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D125" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E125" s="5" t="str"/>
+      <x:c r="E125" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F125" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G125" s="5" t="str"/>
+      <x:c r="H125" s="5" t="str">
+        <x:v>PR-058</x:v>
+      </x:c>
+      <x:c r="I125" s="5" t="str">
+        <x:v>ERJ-2RKF4702X</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="31" customHeight="1">
       <x:c r="A126" s="5" t="str">
         <x:v>R26</x:v>
       </x:c>
       <x:c r="B126" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C126" s="5" t="str">
+        <x:v>ERJ-2RKF4701X</x:v>
+      </x:c>
+      <x:c r="D126" s="5" t="str">
         <x:v>4.7 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C126" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D126" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E126" s="5" t="str"/>
+      <x:c r="E126" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F126" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G126" s="5" t="str"/>
+      <x:c r="H126" s="5" t="str">
+        <x:v>PR-056</x:v>
+      </x:c>
+      <x:c r="I126" s="5" t="str">
+        <x:v>ERJ-2RKF4701X</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" ht="31" customHeight="1">
       <x:c r="A127" s="5" t="str">
         <x:v>R27</x:v>
       </x:c>
       <x:c r="B127" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C127" s="5" t="str">
+        <x:v>ERJ-2RKF4702X</x:v>
+      </x:c>
+      <x:c r="D127" s="5" t="str">
         <x:v>47 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C127" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D127" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E127" s="5" t="str"/>
+      <x:c r="E127" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F127" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G127" s="5" t="str"/>
+      <x:c r="H127" s="5" t="str">
+        <x:v>PR-058</x:v>
+      </x:c>
+      <x:c r="I127" s="5" t="str">
+        <x:v>ERJ-2RKF4702X</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" ht="31" customHeight="1">
       <x:c r="A128" s="5" t="str">
         <x:v>R28</x:v>
       </x:c>
       <x:c r="B128" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C128" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D128" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C128" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D128" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E128" s="5" t="str"/>
+      <x:c r="E128" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F128" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G128" s="5" t="str"/>
+      <x:c r="H128" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I128" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="31" customHeight="1">
       <x:c r="A129" s="5" t="str">
         <x:v>R29</x:v>
       </x:c>
       <x:c r="B129" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C129" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D129" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C129" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D129" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E129" s="5" t="str"/>
+      <x:c r="E129" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F129" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G129" s="5" t="str"/>
+      <x:c r="H129" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I129" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="31" customHeight="1">
       <x:c r="A130" s="5" t="str">
         <x:v>R30</x:v>
       </x:c>
       <x:c r="B130" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C130" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D130" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C130" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D130" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E130" s="5" t="str"/>
+      <x:c r="E130" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F130" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G130" s="5" t="str"/>
+      <x:c r="H130" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I130" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="31" customHeight="1">
       <x:c r="A131" s="5" t="str">
         <x:v>R31</x:v>
       </x:c>
       <x:c r="B131" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C131" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D131" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C131" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D131" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E131" s="5" t="str"/>
+      <x:c r="E131" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F131" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G131" s="5" t="str"/>
+      <x:c r="H131" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I131" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" ht="31" customHeight="1">
       <x:c r="A132" s="5" t="str">
         <x:v>R32</x:v>
       </x:c>
       <x:c r="B132" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C132" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D132" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C132" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D132" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E132" s="5" t="str"/>
+      <x:c r="E132" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F132" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G132" s="5" t="str"/>
+      <x:c r="H132" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I132" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" ht="31" customHeight="1">
       <x:c r="A133" s="5" t="str">
         <x:v>R33</x:v>
       </x:c>
       <x:c r="B133" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C133" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D133" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C133" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D133" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E133" s="5" t="str"/>
+      <x:c r="E133" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F133" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G133" s="5" t="str"/>
+      <x:c r="H133" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I133" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" ht="31" customHeight="1">
       <x:c r="A134" s="5" t="str">
         <x:v>R34</x:v>
       </x:c>
       <x:c r="B134" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C134" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D134" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C134" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D134" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E134" s="5" t="str"/>
+      <x:c r="E134" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F134" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G134" s="5" t="str"/>
+      <x:c r="H134" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I134" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="135" ht="31" customHeight="1">
       <x:c r="A135" s="5" t="str">
         <x:v>R35</x:v>
       </x:c>
       <x:c r="B135" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C135" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D135" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C135" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D135" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E135" s="5" t="str"/>
+      <x:c r="E135" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F135" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G135" s="5" t="str"/>
+      <x:c r="H135" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I135" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" ht="31" customHeight="1">
       <x:c r="A136" s="5" t="str">
         <x:v>R36</x:v>
       </x:c>
       <x:c r="B136" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C136" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D136" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C136" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D136" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E136" s="5" t="str"/>
+      <x:c r="E136" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F136" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G136" s="5" t="str"/>
+      <x:c r="H136" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I136" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="31" customHeight="1">
       <x:c r="A137" s="5" t="str">
         <x:v>R37</x:v>
       </x:c>
       <x:c r="B137" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C137" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D137" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C137" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D137" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E137" s="5" t="str"/>
+      <x:c r="E137" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F137" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G137" s="5" t="str"/>
+      <x:c r="H137" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I137" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="138" ht="31" customHeight="1">
       <x:c r="A138" s="5" t="str">
         <x:v>R38</x:v>
       </x:c>
       <x:c r="B138" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C138" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
+      <x:c r="D138" s="5" t="str">
         <x:v>1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C138" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D138" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E138" s="5" t="str"/>
+      <x:c r="E138" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F138" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G138" s="5" t="str"/>
+      <x:c r="H138" s="5" t="str">
+        <x:v>PR-046</x:v>
+      </x:c>
+      <x:c r="I138" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" ht="31" customHeight="1">
       <x:c r="A139" s="5" t="str">
         <x:v>R39</x:v>
       </x:c>
       <x:c r="B139" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C139" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D139" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C139" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D139" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E139" s="5" t="str"/>
+      <x:c r="E139" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F139" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G139" s="5" t="str"/>
+      <x:c r="H139" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I139" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="140" ht="31" customHeight="1">
       <x:c r="A140" s="5" t="str">
         <x:v>R40</x:v>
       </x:c>
       <x:c r="B140" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C140" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D140" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C140" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D140" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E140" s="5" t="str"/>
+      <x:c r="E140" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F140" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G140" s="5" t="str"/>
+      <x:c r="H140" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I140" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="141" ht="31" customHeight="1">
       <x:c r="A141" s="5" t="str">
         <x:v>R41</x:v>
       </x:c>
       <x:c r="B141" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C141" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
+      <x:c r="D141" s="5" t="str">
         <x:v>1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C141" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D141" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E141" s="5" t="str"/>
+      <x:c r="E141" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F141" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G141" s="5" t="str"/>
+      <x:c r="H141" s="5" t="str">
+        <x:v>PR-046</x:v>
+      </x:c>
+      <x:c r="I141" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
     </x:row>
     <x:row r="142" ht="31" customHeight="1">
       <x:c r="A142" s="5" t="str">
         <x:v>R42</x:v>
       </x:c>
       <x:c r="B142" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C142" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D142" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C142" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D142" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E142" s="5" t="str"/>
+      <x:c r="E142" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F142" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G142" s="5" t="str"/>
+      <x:c r="H142" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I142" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="143" ht="31" customHeight="1">
       <x:c r="A143" s="5" t="str">
         <x:v>R43</x:v>
       </x:c>
       <x:c r="B143" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C143" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D143" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C143" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D143" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E143" s="5" t="str"/>
+      <x:c r="E143" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F143" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G143" s="5" t="str"/>
+      <x:c r="H143" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I143" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" ht="31" customHeight="1">
       <x:c r="A144" s="5" t="str">
         <x:v>R44</x:v>
       </x:c>
       <x:c r="B144" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C144" s="5" t="str">
+        <x:v>ERJ-2RKF4702X</x:v>
+      </x:c>
+      <x:c r="D144" s="5" t="str">
         <x:v>47 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C144" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D144" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E144" s="5" t="str"/>
+      <x:c r="E144" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F144" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G144" s="5" t="str"/>
+      <x:c r="H144" s="5" t="str">
+        <x:v>PR-058</x:v>
+      </x:c>
+      <x:c r="I144" s="5" t="str">
+        <x:v>ERJ-2RKF4702X</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" ht="31" customHeight="1">
       <x:c r="A145" s="5" t="str">
         <x:v>R45</x:v>
       </x:c>
       <x:c r="B145" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C145" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D145" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C145" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D145" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E145" s="5" t="str"/>
+      <x:c r="E145" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F145" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G145" s="5" t="str"/>
+      <x:c r="H145" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I145" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="31" customHeight="1">
       <x:c r="A146" s="5" t="str">
         <x:v>R46</x:v>
       </x:c>
       <x:c r="B146" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C146" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D146" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C146" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D146" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E146" s="5" t="str"/>
+      <x:c r="E146" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F146" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G146" s="5" t="str"/>
+      <x:c r="H146" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I146" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" ht="31" customHeight="1">
       <x:c r="A147" s="5" t="str">
         <x:v>R47</x:v>
       </x:c>
       <x:c r="B147" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C147" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D147" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C147" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D147" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E147" s="5" t="str"/>
+      <x:c r="E147" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F147" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G147" s="5" t="str"/>
+      <x:c r="H147" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I147" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="148" ht="31" customHeight="1">
       <x:c r="A148" s="5" t="str">
         <x:v>R48</x:v>
       </x:c>
       <x:c r="B148" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C148" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D148" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C148" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D148" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E148" s="5" t="str"/>
+      <x:c r="E148" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F148" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G148" s="5" t="str"/>
+      <x:c r="H148" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I148" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" ht="31" customHeight="1">
       <x:c r="A149" s="5" t="str">
         <x:v>R49</x:v>
       </x:c>
       <x:c r="B149" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C149" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D149" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C149" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D149" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E149" s="5" t="str"/>
+      <x:c r="E149" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F149" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G149" s="5" t="str"/>
+      <x:c r="H149" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I149" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="31" customHeight="1">
       <x:c r="A150" s="5" t="str">
         <x:v>R50</x:v>
       </x:c>
       <x:c r="B150" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C150" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D150" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C150" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D150" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E150" s="5" t="str"/>
+      <x:c r="E150" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F150" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G150" s="5" t="str"/>
+      <x:c r="H150" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I150" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" ht="31" customHeight="1">
       <x:c r="A151" s="5" t="str">
         <x:v>R51</x:v>
       </x:c>
       <x:c r="B151" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C151" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D151" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C151" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D151" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E151" s="5" t="str"/>
+      <x:c r="E151" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F151" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G151" s="5" t="str"/>
+      <x:c r="H151" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I151" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" ht="31" customHeight="1">
       <x:c r="A152" s="5" t="str">
         <x:v>R52</x:v>
       </x:c>
       <x:c r="B152" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C152" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D152" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C152" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D152" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E152" s="5" t="str"/>
+      <x:c r="E152" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F152" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G152" s="5" t="str"/>
+      <x:c r="H152" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I152" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" ht="31" customHeight="1">
       <x:c r="A153" s="5" t="str">
         <x:v>R53</x:v>
       </x:c>
       <x:c r="B153" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C153" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D153" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C153" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D153" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E153" s="5" t="str"/>
+      <x:c r="E153" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F153" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G153" s="5" t="str"/>
+      <x:c r="H153" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I153" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" ht="31" customHeight="1">
       <x:c r="A154" s="5" t="str">
         <x:v>R54</x:v>
       </x:c>
       <x:c r="B154" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C154" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D154" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C154" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D154" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E154" s="5" t="str"/>
+      <x:c r="E154" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F154" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G154" s="5" t="str"/>
+      <x:c r="H154" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I154" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="155" ht="31" customHeight="1">
       <x:c r="A155" s="5" t="str">
         <x:v>R55</x:v>
       </x:c>
       <x:c r="B155" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C155" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D155" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C155" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D155" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E155" s="5" t="str"/>
+      <x:c r="E155" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F155" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G155" s="5" t="str"/>
+      <x:c r="H155" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I155" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="156" ht="31" customHeight="1">
       <x:c r="A156" s="5" t="str">
         <x:v>R56</x:v>
       </x:c>
       <x:c r="B156" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C156" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D156" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C156" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D156" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E156" s="5" t="str"/>
+      <x:c r="E156" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F156" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G156" s="5" t="str"/>
+      <x:c r="H156" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I156" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="157" ht="31" customHeight="1">
       <x:c r="A157" s="5" t="str">
         <x:v>R57</x:v>
       </x:c>
       <x:c r="B157" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C157" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D157" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C157" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D157" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E157" s="5" t="str"/>
+      <x:c r="E157" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F157" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G157" s="5" t="str"/>
+      <x:c r="H157" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I157" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="158" ht="31" customHeight="1">
       <x:c r="A158" s="5" t="str">
         <x:v>R58</x:v>
       </x:c>
       <x:c r="B158" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C158" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D158" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C158" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D158" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E158" s="5" t="str"/>
+      <x:c r="E158" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F158" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G158" s="5" t="str"/>
+      <x:c r="H158" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I158" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="159" ht="31" customHeight="1">
       <x:c r="A159" s="5" t="str">
         <x:v>R59</x:v>
       </x:c>
       <x:c r="B159" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C159" s="5" t="str">
+        <x:v>ERJ-2GEJ561X</x:v>
+      </x:c>
+      <x:c r="D159" s="5" t="str">
         <x:v>560 Ohm 5% 0.1 W</x:v>
       </x:c>
-      <x:c r="C159" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D159" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E159" s="5" t="str"/>
+      <x:c r="E159" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F159" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G159" s="5" t="str"/>
+      <x:c r="H159" s="5" t="str">
+        <x:v>PR-045</x:v>
+      </x:c>
+      <x:c r="I159" s="5" t="str">
+        <x:v>ERJ-2GEJ561X</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" ht="31" customHeight="1">
       <x:c r="A160" s="5" t="str">
         <x:v>R60</x:v>
       </x:c>
       <x:c r="B160" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C160" s="5" t="str">
+        <x:v>ERJ-2GEJ104X</x:v>
+      </x:c>
+      <x:c r="D160" s="5" t="str">
         <x:v>100 kOhm 5% 0.1 W</x:v>
       </x:c>
-      <x:c r="C160" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D160" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E160" s="5" t="str"/>
+      <x:c r="E160" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F160" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G160" s="5" t="str"/>
+      <x:c r="H160" s="5" t="str">
+        <x:v>PR-044</x:v>
+      </x:c>
+      <x:c r="I160" s="5" t="str">
+        <x:v>ERJ-2GEJ104X</x:v>
+      </x:c>
     </x:row>
     <x:row r="161" ht="31" customHeight="1">
       <x:c r="A161" s="5" t="str">
         <x:v>R61</x:v>
       </x:c>
       <x:c r="B161" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C161" s="5" t="str">
+        <x:v>ERJ-2GEJ104X</x:v>
+      </x:c>
+      <x:c r="D161" s="5" t="str">
         <x:v>100 kOhm 5% 0.1 W</x:v>
       </x:c>
-      <x:c r="C161" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D161" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E161" s="5" t="str"/>
+      <x:c r="E161" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F161" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G161" s="5" t="str"/>
+      <x:c r="H161" s="5" t="str">
+        <x:v>PR-044</x:v>
+      </x:c>
+      <x:c r="I161" s="5" t="str">
+        <x:v>ERJ-2GEJ104X</x:v>
+      </x:c>
     </x:row>
     <x:row r="162" ht="31" customHeight="1">
       <x:c r="A162" s="5" t="str">
         <x:v>R62</x:v>
       </x:c>
       <x:c r="B162" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C162" s="5" t="str">
+        <x:v>ERJ-8GEYJ100V</x:v>
+      </x:c>
+      <x:c r="D162" s="5" t="str">
         <x:v>10 Ohm 5% 0.25 W</x:v>
       </x:c>
-      <x:c r="C162" s="5" t="str">
+      <x:c r="E162" s="5" t="str">
         <x:v>Resistor_SMD:R_1206_3216Metric</x:v>
       </x:c>
-      <x:c r="D162" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E162" s="5" t="str"/>
+      <x:c r="F162" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G162" s="5" t="str"/>
+      <x:c r="H162" s="5" t="str">
+        <x:v>PR-060</x:v>
+      </x:c>
+      <x:c r="I162" s="5" t="str">
+        <x:v>ERJ-8GEYJ100V</x:v>
+      </x:c>
     </x:row>
     <x:row r="163" ht="31" customHeight="1">
       <x:c r="A163" s="5" t="str">
         <x:v>R63</x:v>
       </x:c>
       <x:c r="B163" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C163" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D163" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C163" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D163" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E163" s="5" t="str"/>
+      <x:c r="E163" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F163" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G163" s="5" t="str"/>
+      <x:c r="H163" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I163" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" ht="31" customHeight="1">
       <x:c r="A164" s="5" t="str">
         <x:v>R64</x:v>
       </x:c>
       <x:c r="B164" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C164" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D164" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C164" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D164" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E164" s="5" t="str"/>
+      <x:c r="E164" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F164" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G164" s="5" t="str"/>
+      <x:c r="H164" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I164" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="165" ht="31" customHeight="1">
       <x:c r="A165" s="5" t="str">
         <x:v>R65</x:v>
       </x:c>
       <x:c r="B165" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C165" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D165" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C165" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D165" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E165" s="5" t="str"/>
+      <x:c r="E165" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F165" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G165" s="5" t="str"/>
+      <x:c r="H165" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I165" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="166" ht="31" customHeight="1">
       <x:c r="A166" s="5" t="str">
         <x:v>R66</x:v>
       </x:c>
       <x:c r="B166" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C166" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D166" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C166" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D166" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E166" s="5" t="str"/>
+      <x:c r="E166" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F166" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G166" s="5" t="str"/>
+      <x:c r="H166" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I166" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="167" ht="31" customHeight="1">
       <x:c r="A167" s="5" t="str">
         <x:v>R67</x:v>
       </x:c>
       <x:c r="B167" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C167" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D167" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C167" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D167" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E167" s="5" t="str"/>
+      <x:c r="E167" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F167" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G167" s="5" t="str"/>
+      <x:c r="H167" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I167" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="168" ht="31" customHeight="1">
       <x:c r="A168" s="5" t="str">
         <x:v>R68</x:v>
       </x:c>
       <x:c r="B168" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C168" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D168" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C168" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D168" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E168" s="5" t="str"/>
+      <x:c r="E168" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F168" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G168" s="5" t="str"/>
+      <x:c r="H168" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I168" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="169" ht="31" customHeight="1">
       <x:c r="A169" s="5" t="str">
         <x:v>R69</x:v>
       </x:c>
       <x:c r="B169" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C169" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D169" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C169" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D169" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E169" s="5" t="str"/>
+      <x:c r="E169" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F169" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G169" s="5" t="str"/>
+      <x:c r="H169" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I169" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="170" ht="31" customHeight="1">
       <x:c r="A170" s="5" t="str">
         <x:v>R70</x:v>
       </x:c>
       <x:c r="B170" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C170" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D170" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C170" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D170" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E170" s="5" t="str"/>
+      <x:c r="E170" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F170" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G170" s="5" t="str"/>
+      <x:c r="H170" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I170" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="171" ht="31" customHeight="1">
       <x:c r="A171" s="5" t="str">
         <x:v>R71</x:v>
       </x:c>
       <x:c r="B171" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C171" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D171" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C171" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D171" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E171" s="5" t="str"/>
+      <x:c r="E171" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F171" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G171" s="5" t="str"/>
+      <x:c r="H171" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I171" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="172" ht="31" customHeight="1">
       <x:c r="A172" s="5" t="str">
         <x:v>R72</x:v>
       </x:c>
       <x:c r="B172" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C172" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D172" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C172" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D172" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E172" s="5" t="str"/>
+      <x:c r="E172" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F172" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G172" s="5" t="str"/>
+      <x:c r="H172" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I172" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" ht="31" customHeight="1">
       <x:c r="A173" s="5" t="str">
         <x:v>R73</x:v>
       </x:c>
       <x:c r="B173" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C173" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D173" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C173" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D173" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E173" s="5" t="str"/>
+      <x:c r="E173" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F173" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G173" s="5" t="str"/>
+      <x:c r="H173" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I173" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" ht="31" customHeight="1">
       <x:c r="A174" s="5" t="str">
         <x:v>R74</x:v>
       </x:c>
       <x:c r="B174" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C174" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D174" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C174" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D174" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E174" s="5" t="str"/>
+      <x:c r="E174" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F174" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G174" s="5" t="str"/>
+      <x:c r="H174" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I174" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="175" ht="31" customHeight="1">
       <x:c r="A175" s="5" t="str">
         <x:v>R75</x:v>
       </x:c>
       <x:c r="B175" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C175" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D175" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C175" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D175" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E175" s="5" t="str"/>
+      <x:c r="E175" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F175" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G175" s="5" t="str"/>
+      <x:c r="H175" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I175" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="176" ht="31" customHeight="1">
       <x:c r="A176" s="5" t="str">
         <x:v>R76</x:v>
       </x:c>
       <x:c r="B176" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C176" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D176" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C176" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D176" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E176" s="5" t="str"/>
+      <x:c r="E176" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F176" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G176" s="5" t="str"/>
+      <x:c r="H176" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I176" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="177" ht="31" customHeight="1">
       <x:c r="A177" s="5" t="str">
         <x:v>R77</x:v>
       </x:c>
       <x:c r="B177" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C177" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D177" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C177" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D177" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E177" s="5" t="str"/>
+      <x:c r="E177" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F177" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G177" s="5" t="str"/>
+      <x:c r="H177" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I177" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="178" ht="31" customHeight="1">
       <x:c r="A178" s="5" t="str">
         <x:v>R78</x:v>
       </x:c>
       <x:c r="B178" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C178" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D178" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C178" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D178" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E178" s="5" t="str"/>
+      <x:c r="E178" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F178" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G178" s="5" t="str"/>
+      <x:c r="H178" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I178" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="179" ht="31" customHeight="1">
       <x:c r="A179" s="5" t="str">
         <x:v>R79</x:v>
       </x:c>
       <x:c r="B179" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C179" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D179" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C179" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D179" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E179" s="5" t="str"/>
+      <x:c r="E179" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F179" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G179" s="5" t="str"/>
+      <x:c r="H179" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I179" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="180" ht="31" customHeight="1">
       <x:c r="A180" s="5" t="str">
         <x:v>R80</x:v>
       </x:c>
       <x:c r="B180" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C180" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D180" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C180" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D180" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E180" s="5" t="str"/>
+      <x:c r="E180" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F180" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G180" s="5" t="str"/>
+      <x:c r="H180" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I180" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="181" ht="31" customHeight="1">
       <x:c r="A181" s="5" t="str">
         <x:v>R81</x:v>
       </x:c>
       <x:c r="B181" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C181" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D181" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C181" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D181" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E181" s="5" t="str"/>
+      <x:c r="E181" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F181" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G181" s="5" t="str"/>
+      <x:c r="H181" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I181" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="182" ht="31" customHeight="1">
       <x:c r="A182" s="5" t="str">
         <x:v>R82</x:v>
       </x:c>
       <x:c r="B182" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C182" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D182" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C182" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D182" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E182" s="5" t="str"/>
+      <x:c r="E182" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F182" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G182" s="5" t="str"/>
+      <x:c r="H182" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I182" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="183" ht="31" customHeight="1">
       <x:c r="A183" s="5" t="str">
         <x:v>R83</x:v>
       </x:c>
       <x:c r="B183" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C183" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D183" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C183" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D183" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E183" s="5" t="str"/>
+      <x:c r="E183" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F183" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G183" s="5" t="str"/>
+      <x:c r="H183" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I183" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="184" ht="31" customHeight="1">
       <x:c r="A184" s="5" t="str">
         <x:v>R84</x:v>
       </x:c>
       <x:c r="B184" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C184" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D184" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C184" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D184" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E184" s="5" t="str"/>
+      <x:c r="E184" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F184" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G184" s="5" t="str"/>
+      <x:c r="H184" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I184" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="185" ht="31" customHeight="1">
       <x:c r="A185" s="5" t="str">
         <x:v>R85</x:v>
       </x:c>
       <x:c r="B185" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C185" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D185" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C185" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D185" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E185" s="5" t="str"/>
+      <x:c r="E185" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F185" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G185" s="5" t="str"/>
+      <x:c r="H185" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I185" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="186" ht="31" customHeight="1">
       <x:c r="A186" s="5" t="str">
         <x:v>R86</x:v>
       </x:c>
       <x:c r="B186" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C186" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D186" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C186" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D186" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E186" s="5" t="str"/>
+      <x:c r="E186" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F186" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G186" s="5" t="str"/>
+      <x:c r="H186" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I186" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="187" ht="31" customHeight="1">
       <x:c r="A187" s="5" t="str">
         <x:v>R87</x:v>
       </x:c>
       <x:c r="B187" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C187" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D187" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C187" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D187" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E187" s="5" t="str"/>
+      <x:c r="E187" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F187" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G187" s="5" t="str"/>
+      <x:c r="H187" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I187" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="188" ht="31" customHeight="1">
       <x:c r="A188" s="5" t="str">
         <x:v>R88</x:v>
       </x:c>
       <x:c r="B188" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C188" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D188" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C188" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D188" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E188" s="5" t="str"/>
+      <x:c r="E188" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F188" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G188" s="5" t="str"/>
+      <x:c r="H188" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I188" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="189" ht="31" customHeight="1">
       <x:c r="A189" s="5" t="str">
         <x:v>R89</x:v>
       </x:c>
       <x:c r="B189" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C189" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D189" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C189" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D189" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E189" s="5" t="str"/>
+      <x:c r="E189" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F189" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G189" s="5" t="str"/>
+      <x:c r="H189" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I189" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="190" ht="31" customHeight="1">
       <x:c r="A190" s="5" t="str">
         <x:v>R90</x:v>
       </x:c>
       <x:c r="B190" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C190" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D190" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C190" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D190" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E190" s="5" t="str"/>
+      <x:c r="E190" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F190" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G190" s="5" t="str"/>
+      <x:c r="H190" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I190" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="191" ht="31" customHeight="1">
       <x:c r="A191" s="5" t="str">
         <x:v>R91</x:v>
       </x:c>
       <x:c r="B191" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C191" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D191" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C191" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D191" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E191" s="5" t="str"/>
+      <x:c r="E191" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F191" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G191" s="5" t="str"/>
+      <x:c r="H191" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I191" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="192" ht="31" customHeight="1">
       <x:c r="A192" s="5" t="str">
         <x:v>R92</x:v>
       </x:c>
       <x:c r="B192" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C192" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D192" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C192" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D192" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E192" s="5" t="str"/>
+      <x:c r="E192" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F192" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G192" s="5" t="str"/>
+      <x:c r="H192" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I192" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="193" ht="31" customHeight="1">
       <x:c r="A193" s="5" t="str">
         <x:v>R93</x:v>
       </x:c>
       <x:c r="B193" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C193" s="5" t="str">
+        <x:v>ERJ-2RKF5101X</x:v>
+      </x:c>
+      <x:c r="D193" s="5" t="str">
         <x:v>5.1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C193" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D193" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E193" s="5" t="str"/>
+      <x:c r="E193" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F193" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G193" s="5" t="str"/>
+      <x:c r="H193" s="5" t="str">
+        <x:v>PR-059</x:v>
+      </x:c>
+      <x:c r="I193" s="5" t="str">
+        <x:v>ERJ-2RKF5101X</x:v>
+      </x:c>
     </x:row>
     <x:row r="194" ht="31" customHeight="1">
       <x:c r="A194" s="5" t="str">
         <x:v>R94</x:v>
       </x:c>
       <x:c r="B194" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C194" s="5" t="str">
+        <x:v>ERJ-2RKF5101X</x:v>
+      </x:c>
+      <x:c r="D194" s="5" t="str">
         <x:v>5.1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C194" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D194" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E194" s="5" t="str"/>
+      <x:c r="E194" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F194" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G194" s="5" t="str"/>
+      <x:c r="H194" s="5" t="str">
+        <x:v>PR-059</x:v>
+      </x:c>
+      <x:c r="I194" s="5" t="str">
+        <x:v>ERJ-2RKF5101X</x:v>
+      </x:c>
     </x:row>
     <x:row r="195" ht="31" customHeight="1">
       <x:c r="A195" s="5" t="str">
         <x:v>R95</x:v>
       </x:c>
       <x:c r="B195" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C195" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
+      <x:c r="D195" s="5" t="str">
         <x:v>1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C195" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D195" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E195" s="5" t="str"/>
+      <x:c r="E195" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F195" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G195" s="5" t="str"/>
+      <x:c r="H195" s="5" t="str">
+        <x:v>PR-046</x:v>
+      </x:c>
+      <x:c r="I195" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" ht="31" customHeight="1">
       <x:c r="A196" s="5" t="str">
         <x:v>R96</x:v>
       </x:c>
       <x:c r="B196" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C196" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
+      <x:c r="D196" s="5" t="str">
         <x:v>100 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C196" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D196" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E196" s="5" t="str"/>
+      <x:c r="E196" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F196" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G196" s="5" t="str"/>
+      <x:c r="H196" s="5" t="str">
+        <x:v>PR-051</x:v>
+      </x:c>
+      <x:c r="I196" s="5" t="str">
+        <x:v>ERJ-2RKF1003X</x:v>
+      </x:c>
     </x:row>
     <x:row r="197" ht="31" customHeight="1">
       <x:c r="A197" s="5" t="str">
         <x:v>R97</x:v>
       </x:c>
       <x:c r="B197" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C197" s="5" t="str">
+        <x:v>ERJ-2RKF1004X</x:v>
+      </x:c>
+      <x:c r="D197" s="5" t="str">
         <x:v>1 MOhm 1%</x:v>
       </x:c>
-      <x:c r="C197" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D197" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E197" s="5" t="str"/>
+      <x:c r="E197" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F197" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G197" s="5" t="str"/>
+      <x:c r="H197" s="5" t="str">
+        <x:v>PR-053</x:v>
+      </x:c>
+      <x:c r="I197" s="5" t="str">
+        <x:v>ERJ-2RKF1004X</x:v>
+      </x:c>
     </x:row>
     <x:row r="198" ht="31" customHeight="1">
       <x:c r="A198" s="5" t="str">
         <x:v>R99</x:v>
       </x:c>
       <x:c r="B198" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C198" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
+      <x:c r="D198" s="5" t="str">
         <x:v>10 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C198" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D198" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E198" s="5" t="str"/>
+      <x:c r="E198" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F198" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G198" s="5" t="str"/>
+      <x:c r="H198" s="5" t="str">
+        <x:v>PR-047</x:v>
+      </x:c>
+      <x:c r="I198" s="5" t="str">
+        <x:v>ERJ-2RKF1002X</x:v>
+      </x:c>
     </x:row>
     <x:row r="199" ht="31" customHeight="1">
       <x:c r="A199" s="5" t="str">
         <x:v>R100</x:v>
       </x:c>
       <x:c r="B199" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C199" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
+      <x:c r="D199" s="5" t="str">
         <x:v>1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C199" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D199" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E199" s="5" t="str"/>
+      <x:c r="E199" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F199" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G199" s="5" t="str"/>
+      <x:c r="H199" s="5" t="str">
+        <x:v>PR-046</x:v>
+      </x:c>
+      <x:c r="I199" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
     </x:row>
     <x:row r="200" ht="31" customHeight="1">
       <x:c r="A200" s="5" t="str">
         <x:v>R101</x:v>
       </x:c>
       <x:c r="B200" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C200" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
+      <x:c r="D200" s="5" t="str">
         <x:v>22 Ohm 1%</x:v>
       </x:c>
-      <x:c r="C200" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D200" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E200" s="5" t="str"/>
+      <x:c r="E200" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F200" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G200" s="5" t="str"/>
+      <x:c r="H200" s="5" t="str">
+        <x:v>PR-055</x:v>
+      </x:c>
+      <x:c r="I200" s="5" t="str">
+        <x:v>ERJ-2RKF22R0X</x:v>
+      </x:c>
     </x:row>
     <x:row r="201" ht="31" customHeight="1">
       <x:c r="A201" s="5" t="str">
         <x:v>R102</x:v>
       </x:c>
       <x:c r="B201" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C201" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
+      <x:c r="D201" s="5" t="str">
         <x:v>1 kOhm 1%</x:v>
       </x:c>
-      <x:c r="C201" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D201" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E201" s="5" t="str"/>
+      <x:c r="E201" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F201" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G201" s="5" t="str"/>
+      <x:c r="H201" s="5" t="str">
+        <x:v>PR-046</x:v>
+      </x:c>
+      <x:c r="I201" s="5" t="str">
+        <x:v>ERJ-2RKF1001X</x:v>
+      </x:c>
     </x:row>
     <x:row r="202" ht="31" customHeight="1">
       <x:c r="A202" s="5" t="str">
         <x:v>R103</x:v>
       </x:c>
       <x:c r="B202" s="5" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="C202" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
+      <x:c r="D202" s="5" t="str">
         <x:v>0 Ohm</x:v>
       </x:c>
-      <x:c r="C202" s="5" t="str">
-        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
-      </x:c>
-      <x:c r="D202" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E202" s="5" t="str"/>
+      <x:c r="E202" s="5" t="str">
+        <x:v>Resistor_SMD:R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="F202" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G202" s="5" t="str"/>
+      <x:c r="H202" s="5" t="str">
+        <x:v>PR-040</x:v>
+      </x:c>
+      <x:c r="I202" s="5" t="str">
+        <x:v>ERJ-2GE0R00X</x:v>
+      </x:c>
     </x:row>
     <x:row r="203" ht="31" customHeight="1">
       <x:c r="A203" s="5" t="str">
         <x:v>U1</x:v>
       </x:c>
       <x:c r="B203" s="5" t="str">
+        <x:v>STMicroelectronics</x:v>
+      </x:c>
+      <x:c r="C203" s="5" t="str">
         <x:v>STM32U585VIT6Q</x:v>
       </x:c>
-      <x:c r="C203" s="5" t="str"/>
       <x:c r="D203" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>STM32U585VIT6Q</x:v>
       </x:c>
       <x:c r="E203" s="5" t="str"/>
+      <x:c r="F203" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G203" s="5" t="str"/>
+      <x:c r="H203" s="5" t="str">
+        <x:v>PR-107</x:v>
+      </x:c>
+      <x:c r="I203" s="5" t="str">
+        <x:v>STM32U585VIT6Q</x:v>
+      </x:c>
     </x:row>
     <x:row r="204" ht="31" customHeight="1">
       <x:c r="A204" s="5" t="str">
         <x:v>U2</x:v>
       </x:c>
       <x:c r="B204" s="5" t="str">
+        <x:v>Winbond</x:v>
+      </x:c>
+      <x:c r="C204" s="5" t="str">
         <x:v>W25Q512JVFIQ</x:v>
       </x:c>
-      <x:c r="C204" s="5" t="str"/>
       <x:c r="D204" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>W25Q512JVFIQ</x:v>
       </x:c>
       <x:c r="E204" s="5" t="str"/>
+      <x:c r="F204" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G204" s="5" t="str"/>
+      <x:c r="H204" s="5" t="str">
+        <x:v>PR-122</x:v>
+      </x:c>
+      <x:c r="I204" s="5" t="str">
+        <x:v>W25Q512JVFIQ</x:v>
+      </x:c>
     </x:row>
     <x:row r="205" ht="31" customHeight="1">
       <x:c r="A205" s="5" t="str">
         <x:v>U3</x:v>
       </x:c>
       <x:c r="B205" s="5" t="str">
+        <x:v>STMicroelectronics</x:v>
+      </x:c>
+      <x:c r="C205" s="5" t="str">
         <x:v>LIS2DW12TR</x:v>
       </x:c>
-      <x:c r="C205" s="5" t="str"/>
       <x:c r="D205" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>LIS2DW12TR</x:v>
       </x:c>
       <x:c r="E205" s="5" t="str"/>
+      <x:c r="F205" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G205" s="5" t="str"/>
+      <x:c r="H205" s="5" t="str">
+        <x:v>PR-083</x:v>
+      </x:c>
+      <x:c r="I205" s="5" t="str">
+        <x:v>LIS2DW12TR</x:v>
+      </x:c>
     </x:row>
     <x:row r="206" ht="31" customHeight="1">
       <x:c r="A206" s="5" t="str">
         <x:v>U4</x:v>
       </x:c>
       <x:c r="B206" s="5" t="str">
+        <x:v>STMicroelectronics</x:v>
+      </x:c>
+      <x:c r="C206" s="5" t="str">
         <x:v>STTS22HTR</x:v>
       </x:c>
-      <x:c r="C206" s="5" t="str"/>
       <x:c r="D206" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>STTS22HTR</x:v>
       </x:c>
       <x:c r="E206" s="5" t="str"/>
+      <x:c r="F206" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G206" s="5" t="str"/>
+      <x:c r="H206" s="5" t="str">
+        <x:v>PR-108</x:v>
+      </x:c>
+      <x:c r="I206" s="5" t="str">
+        <x:v>STTS22HTR</x:v>
+      </x:c>
     </x:row>
     <x:row r="207" ht="31" customHeight="1">
       <x:c r="A207" s="5" t="str">
         <x:v>U5</x:v>
       </x:c>
       <x:c r="B207" s="5" t="str">
+        <x:v>Analog Devices</x:v>
+      </x:c>
+      <x:c r="C207" s="5" t="str">
+        <x:v>LT6000IDCB#TRMPBF</x:v>
+      </x:c>
+      <x:c r="D207" s="5" t="str">
         <x:v>Single rail-to-rail low-power op amp</x:v>
       </x:c>
-      <x:c r="C207" s="5" t="str"/>
-      <x:c r="D207" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E207" s="5" t="str"/>
+      <x:c r="F207" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G207" s="5" t="str"/>
+      <x:c r="H207" s="5" t="str">
+        <x:v>PR-088</x:v>
+      </x:c>
+      <x:c r="I207" s="5" t="str">
+        <x:v>LT6000IDCB#TRMPBF</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" ht="31" customHeight="1">
       <x:c r="A208" s="5" t="str">
         <x:v>U6</x:v>
       </x:c>
       <x:c r="B208" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C208" s="5" t="str">
+        <x:v>SN74LVC1G07DBVR</x:v>
+      </x:c>
+      <x:c r="D208" s="5" t="str">
         <x:v>Single non-inverting open-drain buffer</x:v>
       </x:c>
-      <x:c r="C208" s="5" t="str"/>
-      <x:c r="D208" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E208" s="5" t="str"/>
+      <x:c r="F208" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G208" s="5" t="str"/>
+      <x:c r="H208" s="5" t="str">
+        <x:v>PR-105</x:v>
+      </x:c>
+      <x:c r="I208" s="5" t="str">
+        <x:v>SN74LVC1G07DBVR</x:v>
+      </x:c>
     </x:row>
     <x:row r="209" ht="31" customHeight="1">
       <x:c r="A209" s="5" t="str">
         <x:v>U7</x:v>
       </x:c>
       <x:c r="B209" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C209" s="5" t="str">
         <x:v>SN74AXC8T245PWR</x:v>
       </x:c>
-      <x:c r="C209" s="5" t="str"/>
       <x:c r="D209" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>SN74AXC8T245PWR</x:v>
       </x:c>
       <x:c r="E209" s="5" t="str"/>
+      <x:c r="F209" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G209" s="5" t="str"/>
+      <x:c r="H209" s="5" t="str">
+        <x:v>PR-104</x:v>
+      </x:c>
+      <x:c r="I209" s="5" t="str">
+        <x:v>SN74AXC8T245PWR</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" ht="31" customHeight="1">
       <x:c r="A210" s="5" t="str">
         <x:v>U8</x:v>
       </x:c>
       <x:c r="B210" s="5" t="str">
+        <x:v>Quectel</x:v>
+      </x:c>
+      <x:c r="C210" s="5" t="str">
         <x:v>BG95-M3</x:v>
       </x:c>
-      <x:c r="C210" s="5" t="str"/>
       <x:c r="D210" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>BG95-M3</x:v>
       </x:c>
       <x:c r="E210" s="5" t="str"/>
+      <x:c r="F210" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G210" s="5" t="str"/>
+      <x:c r="H210" s="5" t="str">
+        <x:v>PR-024</x:v>
+      </x:c>
+      <x:c r="I210" s="5" t="str">
+        <x:v>BG95-M3</x:v>
+      </x:c>
     </x:row>
     <x:row r="211" ht="31" customHeight="1">
       <x:c r="A211" s="5" t="str">
         <x:v>U9</x:v>
       </x:c>
       <x:c r="B211" s="5" t="str">
+        <x:v>u-blox</x:v>
+      </x:c>
+      <x:c r="C211" s="5" t="str">
         <x:v>MAX-M10S-00B</x:v>
       </x:c>
-      <x:c r="C211" s="5" t="str"/>
       <x:c r="D211" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>MAX-M10S-00B</x:v>
       </x:c>
       <x:c r="E211" s="5" t="str"/>
+      <x:c r="F211" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G211" s="5" t="str"/>
+      <x:c r="H211" s="5" t="str">
+        <x:v>PR-089</x:v>
+      </x:c>
+      <x:c r="I211" s="5" t="str">
+        <x:v>MAX-M10S-00B</x:v>
+      </x:c>
     </x:row>
     <x:row r="212" ht="31" customHeight="1">
       <x:c r="A212" s="5" t="str">
         <x:v>U10</x:v>
       </x:c>
       <x:c r="B212" s="5" t="str">
+        <x:v>Ebyte</x:v>
+      </x:c>
+      <x:c r="C212" s="5" t="str">
         <x:v>E22-900M22S</x:v>
       </x:c>
-      <x:c r="C212" s="5" t="str"/>
       <x:c r="D212" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>E22-900M22S</x:v>
       </x:c>
       <x:c r="E212" s="5" t="str"/>
+      <x:c r="F212" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G212" s="5" t="str"/>
+      <x:c r="H212" s="5" t="str">
+        <x:v>PR-034</x:v>
+      </x:c>
+      <x:c r="I212" s="5" t="str">
+        <x:v>E22-900M22S</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" ht="31" customHeight="1">
       <x:c r="A213" s="5" t="str">
         <x:v>U11</x:v>
       </x:c>
       <x:c r="B213" s="5" t="str">
+        <x:v>Raytac</x:v>
+      </x:c>
+      <x:c r="C213" s="5" t="str">
         <x:v>MDBT50Q-P1MV2</x:v>
       </x:c>
-      <x:c r="C213" s="5" t="str"/>
       <x:c r="D213" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>MDBT50Q-P1MV2</x:v>
       </x:c>
       <x:c r="E213" s="5" t="str"/>
+      <x:c r="F213" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G213" s="5" t="str"/>
+      <x:c r="H213" s="5" t="str">
+        <x:v>PR-090</x:v>
+      </x:c>
+      <x:c r="I213" s="5" t="str">
+        <x:v>MDBT50Q-P1MV2</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" ht="31" customHeight="1">
       <x:c r="A214" s="5" t="str">
         <x:v>U13</x:v>
       </x:c>
       <x:c r="B214" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C214" s="5" t="str">
         <x:v>TS3A27518EPWR</x:v>
       </x:c>
-      <x:c r="C214" s="5" t="str"/>
       <x:c r="D214" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>TS3A27518EPWR</x:v>
       </x:c>
       <x:c r="E214" s="5" t="str"/>
+      <x:c r="F214" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G214" s="5" t="str"/>
+      <x:c r="H214" s="5" t="str">
+        <x:v>PR-118</x:v>
+      </x:c>
+      <x:c r="I214" s="5" t="str">
+        <x:v>TS3A27518EPWR</x:v>
+      </x:c>
     </x:row>
     <x:row r="215" ht="31" customHeight="1">
       <x:c r="A215" s="5" t="str">
         <x:v>U14</x:v>
       </x:c>
       <x:c r="B215" s="5" t="str">
+        <x:v>STMicroelectronics</x:v>
+      </x:c>
+      <x:c r="C215" s="5" t="str">
         <x:v>ESDALC6V1-5P6</x:v>
       </x:c>
-      <x:c r="C215" s="5" t="str"/>
       <x:c r="D215" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>ESDALC6V1-5P6</x:v>
       </x:c>
       <x:c r="E215" s="5" t="str"/>
+      <x:c r="F215" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G215" s="5" t="str"/>
+      <x:c r="H215" s="5" t="str">
+        <x:v>PR-061</x:v>
+      </x:c>
+      <x:c r="I215" s="5" t="str">
+        <x:v>ESDALC6V1-5P6</x:v>
+      </x:c>
     </x:row>
     <x:row r="216" ht="31" customHeight="1">
       <x:c r="A216" s="5" t="str">
         <x:v>U15</x:v>
       </x:c>
       <x:c r="B216" s="5" t="str">
+        <x:v>STMicroelectronics</x:v>
+      </x:c>
+      <x:c r="C216" s="5" t="str">
         <x:v>ESDALC6V1-5P6</x:v>
       </x:c>
-      <x:c r="C216" s="5" t="str"/>
       <x:c r="D216" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>ESDALC6V1-5P6</x:v>
       </x:c>
       <x:c r="E216" s="5" t="str"/>
+      <x:c r="F216" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G216" s="5" t="str"/>
+      <x:c r="H216" s="5" t="str">
+        <x:v>PR-061</x:v>
+      </x:c>
+      <x:c r="I216" s="5" t="str">
+        <x:v>ESDALC6V1-5P6</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" ht="31" customHeight="1">
       <x:c r="A217" s="5" t="str">
         <x:v>U16</x:v>
       </x:c>
       <x:c r="B217" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C217" s="5" t="str">
         <x:v>SN74AXC8T245PWR</x:v>
       </x:c>
-      <x:c r="C217" s="5" t="str"/>
       <x:c r="D217" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>SN74AXC8T245PWR</x:v>
       </x:c>
       <x:c r="E217" s="5" t="str"/>
+      <x:c r="F217" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G217" s="5" t="str"/>
+      <x:c r="H217" s="5" t="str">
+        <x:v>PR-104</x:v>
+      </x:c>
+      <x:c r="I217" s="5" t="str">
+        <x:v>SN74AXC8T245PWR</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" ht="31" customHeight="1">
       <x:c r="A218" s="5" t="str">
         <x:v>U17</x:v>
       </x:c>
       <x:c r="B218" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C218" s="5" t="str">
         <x:v>SN74LVC32APWR</x:v>
       </x:c>
-      <x:c r="C218" s="5" t="str"/>
       <x:c r="D218" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>SN74LVC32APWR</x:v>
       </x:c>
       <x:c r="E218" s="5" t="str"/>
+      <x:c r="F218" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G218" s="5" t="str"/>
+      <x:c r="H218" s="5" t="str">
+        <x:v>PR-106</x:v>
+      </x:c>
+      <x:c r="I218" s="5" t="str">
+        <x:v>SN74LVC32APWR</x:v>
+      </x:c>
     </x:row>
     <x:row r="219" ht="31" customHeight="1">
       <x:c r="A219" s="5" t="str">
         <x:v>U18</x:v>
       </x:c>
       <x:c r="B219" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C219" s="5" t="str">
         <x:v>SN74AXC1T45DRLR</x:v>
       </x:c>
-      <x:c r="C219" s="5" t="str"/>
       <x:c r="D219" s="5" t="str">
-        <x:v>1</x:v>
+        <x:v>SN74AXC1T45DRLR</x:v>
       </x:c>
       <x:c r="E219" s="5" t="str"/>
+      <x:c r="F219" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G219" s="5" t="str"/>
+      <x:c r="H219" s="5" t="str">
+        <x:v>PR-103</x:v>
+      </x:c>
+      <x:c r="I219" s="5" t="str">
+        <x:v>SN74AXC1T45DRLR</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="31" customHeight="1">
       <x:c r="A220" s="5" t="str">
         <x:v>U19</x:v>
       </x:c>
       <x:c r="B220" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C220" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D220" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C220" s="5" t="str"/>
-      <x:c r="D220" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E220" s="5" t="str"/>
+      <x:c r="F220" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G220" s="5" t="str"/>
+      <x:c r="H220" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I220" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="31" customHeight="1">
       <x:c r="A221" s="5" t="str">
         <x:v>U20</x:v>
       </x:c>
       <x:c r="B221" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C221" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D221" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C221" s="5" t="str"/>
-      <x:c r="D221" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E221" s="5" t="str"/>
+      <x:c r="F221" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G221" s="5" t="str"/>
+      <x:c r="H221" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I221" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" ht="31" customHeight="1">
       <x:c r="A222" s="5" t="str">
         <x:v>U21</x:v>
       </x:c>
       <x:c r="B222" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C222" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D222" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C222" s="5" t="str"/>
-      <x:c r="D222" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E222" s="5" t="str"/>
+      <x:c r="F222" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G222" s="5" t="str"/>
+      <x:c r="H222" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I222" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="223" ht="31" customHeight="1">
       <x:c r="A223" s="5" t="str">
         <x:v>U22</x:v>
       </x:c>
       <x:c r="B223" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C223" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D223" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C223" s="5" t="str"/>
-      <x:c r="D223" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E223" s="5" t="str"/>
+      <x:c r="F223" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G223" s="5" t="str"/>
+      <x:c r="H223" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I223" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="224" ht="31" customHeight="1">
       <x:c r="A224" s="5" t="str">
         <x:v>U23</x:v>
       </x:c>
       <x:c r="B224" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C224" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D224" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C224" s="5" t="str"/>
-      <x:c r="D224" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E224" s="5" t="str"/>
+      <x:c r="F224" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G224" s="5" t="str"/>
+      <x:c r="H224" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I224" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="225" ht="31" customHeight="1">
       <x:c r="A225" s="5" t="str">
         <x:v>U24</x:v>
       </x:c>
       <x:c r="B225" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C225" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D225" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C225" s="5" t="str"/>
-      <x:c r="D225" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E225" s="5" t="str"/>
+      <x:c r="F225" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G225" s="5" t="str"/>
+      <x:c r="H225" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I225" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="226" ht="31" customHeight="1">
       <x:c r="A226" s="5" t="str">
         <x:v>U25</x:v>
       </x:c>
       <x:c r="B226" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C226" s="5" t="str">
+        <x:v>TPD2EUSB30DRTR</x:v>
+      </x:c>
+      <x:c r="D226" s="5" t="str">
         <x:v>2 channel 0.7 pF USB ESD</x:v>
       </x:c>
-      <x:c r="C226" s="5" t="str"/>
-      <x:c r="D226" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E226" s="5" t="str"/>
+      <x:c r="F226" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G226" s="5" t="str"/>
+      <x:c r="H226" s="5" t="str">
+        <x:v>PR-115</x:v>
+      </x:c>
+      <x:c r="I226" s="5" t="str">
+        <x:v>TPD2EUSB30DRTR</x:v>
+      </x:c>
     </x:row>
     <x:row r="227" ht="31" customHeight="1">
       <x:c r="A227" s="5" t="str">
         <x:v>U26</x:v>
       </x:c>
       <x:c r="B227" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C227" s="5" t="str">
+        <x:v>TPD2EUSB30DRTR</x:v>
+      </x:c>
+      <x:c r="D227" s="5" t="str">
         <x:v>2 channel 0.7 pF USB ESD</x:v>
       </x:c>
-      <x:c r="C227" s="5" t="str"/>
-      <x:c r="D227" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E227" s="5" t="str"/>
+      <x:c r="F227" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G227" s="5" t="str"/>
+      <x:c r="H227" s="5" t="str">
+        <x:v>PR-115</x:v>
+      </x:c>
+      <x:c r="I227" s="5" t="str">
+        <x:v>TPD2EUSB30DRTR</x:v>
+      </x:c>
     </x:row>
     <x:row r="228" ht="31" customHeight="1">
       <x:c r="A228" s="5" t="str">
         <x:v>U27</x:v>
       </x:c>
       <x:c r="B228" s="5" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="C228" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
+      <x:c r="D228" s="5" t="str">
         <x:v>4 channel 0.5 pF ESD</x:v>
       </x:c>
-      <x:c r="C228" s="5" t="str"/>
-      <x:c r="D228" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E228" s="5" t="str"/>
+      <x:c r="F228" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G228" s="5" t="str"/>
+      <x:c r="H228" s="5" t="str">
+        <x:v>PR-116</x:v>
+      </x:c>
+      <x:c r="I228" s="5" t="str">
+        <x:v>TPD4E05U06DQAR</x:v>
+      </x:c>
     </x:row>
     <x:row r="229" ht="31" customHeight="1">
       <x:c r="A229" s="5" t="str">
         <x:v>X1</x:v>
       </x:c>
       <x:c r="B229" s="5" t="str">
+        <x:v>SiTime</x:v>
+      </x:c>
+      <x:c r="C229" s="5" t="str">
+        <x:v>SiT1552AI-JE-DCC-32.768D</x:v>
+      </x:c>
+      <x:c r="D229" s="5" t="str">
         <x:v>32.768 kHz full-swing LVCMOS</x:v>
       </x:c>
-      <x:c r="C229" s="5" t="str"/>
-      <x:c r="D229" s="5" t="str">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="E229" s="5" t="str"/>
+      <x:c r="F229" s="5" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G229" s="5" t="str"/>
+      <x:c r="H229" s="5" t="str">
+        <x:v>PR-110</x:v>
+      </x:c>
+      <x:c r="I229" s="5" t="str">
+        <x:v>SiT1552AI-JE-DCC-32.768D</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A1:I1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/releases/evt-pre-20/2026-09-30-rev-d/Заказ_плат_и_монтаж/00_Условия_передачи/BOM_плат_для_монтажа.xlsx
+++ b/releases/evt-pre-20/2026-09-30-rev-d/Заказ_плат_и_монтаж/00_Условия_передачи/BOM_плат_для_монтажа.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR BOM" sheetId="1" r:id="Rbf71a3b4f4b14778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR DNP" sheetId="2" r:id="R503dcbdc3f0144e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MIC BOM" sheetId="3" r:id="R6e1d367e3e2d4808"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MAIN BOM" sheetId="4" r:id="R79aa01736290445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="5" r:id="R4e421414b9864b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR BOM" sheetId="1" r:id="Rf672952b1c7b4919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-PWR DNP" sheetId="2" r:id="R07f1b1dca931430e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MIC BOM" sheetId="3" r:id="Rc2291683610d4e2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB-MAIN BOM" sheetId="4" r:id="Rec5f936d12dc4de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="5" r:id="R26cd351c6ac743c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7403,7 +7403,7 @@
         <x:v>Монтаж / Assembly</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Первый образец / First article</x:v>
+        <x:v>Выборка после партии / Post-lot sample</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
         <x:v>Статус / Status</x:v>
@@ -7414,7 +7414,7 @@
         <x:v>PCB-MAIN</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>22 PCBA</x:v>
+        <x:v>22 PCBA, one full lot</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
         <x:v>PCB-MAIN BOM, DNP, off-board</x:v>
@@ -7423,10 +7423,10 @@
         <x:v>227 PCBA placements; 15 DNP; U12 off-board</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>2 изделия / units</x:v>
+        <x:v>2 units after build</x:v>
       </x:c>
       <x:c r="F3" s="5" t="str">
-        <x:v>DRC 0; unconnected 0; ERC 0; fab DFM and stack confirmation</x:v>
+        <x:v>No pause; DFM, stack and 76 POFV before panel</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31" customHeight="1">
@@ -7434,7 +7434,7 @@
         <x:v>PCB-PWR</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>22 PCBA</x:v>
+        <x:v>22 PCBA, one full lot</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>44 fitted; 5 DNP; 3 copper net ties</x:v>
@@ -7443,10 +7443,10 @@
         <x:v>Use position CSV and RU/EN assembly drawing</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>2 изделия / units</x:v>
+        <x:v>2 units after build</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>Order authorized; fab DFM and stack confirmation</x:v>
+        <x:v>No pause; fab DFM and stack confirmation</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="31" customHeight="1">
@@ -7454,7 +7454,7 @@
         <x:v>PCB-MIC Rev B</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>80 PCBA</x:v>
+        <x:v>80 PCBA, one full lot</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>4 fitted per board</x:v>
@@ -7463,10 +7463,10 @@
         <x:v>Acoustic port Ø0.8 NPTH; MK1 stencil controlled</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>1 board/panel → remaining 79</x:v>
+        <x:v>1 board/panel after build</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>Review B ACCEPT CONTROLLED FIRST ARTICLE</x:v>
+        <x:v>Customer schedule supersedes Review B pause only</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
